--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119783553</v>
+        <v>119803900</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79652</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1026</v>
+        <v>229504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 6, Vg</t>
+          <t>Middagsmärket 1:1 pos 8, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432336</v>
+        <v>431942</v>
       </c>
       <c r="R2" t="n">
-        <v>6427848</v>
+        <v>6427740</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -776,12 +768,12 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -791,7 +783,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -809,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119803848</v>
+        <v>119783315</v>
       </c>
       <c r="B3" t="n">
-        <v>94195</v>
+        <v>79035</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,42 +813,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2755</v>
+        <v>1026</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggsprötmossa</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eurhynchium striatum</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 7, Vg</t>
+          <t>Middagsmärket 1:1 pos 6, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>431908</v>
+        <v>432336</v>
       </c>
       <c r="R3" t="n">
-        <v>6427794</v>
+        <v>6427848</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,9 +888,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -916,7 +931,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119783544</v>
+        <v>119783430</v>
       </c>
       <c r="B4" t="n">
         <v>79607</v>
@@ -955,14 +970,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 5, Vg</t>
+          <t>Middagsmärket 1:1 pos 3, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432321</v>
+        <v>432303</v>
       </c>
       <c r="R4" t="n">
-        <v>6427859</v>
+        <v>6427851</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1006,26 +1021,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1042,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119803994</v>
+        <v>119803848</v>
       </c>
       <c r="B5" t="n">
-        <v>79567</v>
+        <v>94195</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,37 +1053,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>2755</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skuggsprötmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Eurhynchium striatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 10, Vg</t>
+          <t>Middagsmärket 1:1 pos 7, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432217</v>
+        <v>431908</v>
       </c>
       <c r="R5" t="n">
-        <v>6427776</v>
+        <v>6427794</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1148,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119803920</v>
+        <v>119783586</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
+        <v>79511</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,41 +1156,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 9, Vg</t>
+          <t>Middagsmärket 1:1 pos 6, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>431951</v>
+        <v>432336</v>
       </c>
       <c r="R6" t="n">
-        <v>6427754</v>
+        <v>6427848</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1241,12 +1245,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>skogsek (aggregat)</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Quercus robur agg.</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1256,7 +1260,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Quercus robur agg.</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1274,7 +1278,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119783475</v>
+        <v>119803994</v>
       </c>
       <c r="B7" t="n">
         <v>79567</v>
@@ -1313,14 +1317,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos4, Vg</t>
+          <t>Middagsmärket 1:1 pos 10, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>432309</v>
+        <v>432217</v>
       </c>
       <c r="R7" t="n">
-        <v>6427862</v>
+        <v>6427776</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1380,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119783430</v>
+        <v>119783475</v>
       </c>
       <c r="B8" t="n">
-        <v>79607</v>
+        <v>79567</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,25 +1396,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1419,14 +1423,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 3, Vg</t>
+          <t>Middagsmärket 1:1 pos4, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>432303</v>
+        <v>432309</v>
       </c>
       <c r="R8" t="n">
-        <v>6427851</v>
+        <v>6427862</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1486,10 +1490,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119783586</v>
+        <v>119803920</v>
       </c>
       <c r="B9" t="n">
-        <v>79511</v>
+        <v>79607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,49 +1502,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 6, Vg</t>
+          <t>Middagsmärket 1:1 pos 9, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>432336</v>
+        <v>431951</v>
       </c>
       <c r="R9" t="n">
-        <v>6427848</v>
+        <v>6427754</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1587,12 +1583,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>skogsek (aggregat)</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Quercus robur agg.</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1602,7 +1598,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Quercus robur agg.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1620,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119803900</v>
+        <v>119783544</v>
       </c>
       <c r="B10" t="n">
-        <v>79652</v>
+        <v>79607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,21 +1632,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229504</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1659,14 +1655,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 8, Vg</t>
+          <t>Middagsmärket 1:1 pos 5, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>431942</v>
+        <v>432321</v>
       </c>
       <c r="R10" t="n">
-        <v>6427740</v>
+        <v>6427859</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1713,12 +1709,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -1728,7 +1724,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1746,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119814486</v>
+        <v>119814579</v>
       </c>
       <c r="B11" t="n">
-        <v>94323</v>
+        <v>79511</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1762,38 +1758,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2813</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 15, Vg</t>
+          <t>Middagsmärket 1:1 pos 16, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>432226</v>
+        <v>432354</v>
       </c>
       <c r="R11" t="n">
-        <v>6427752</v>
+        <v>6427857</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1828,11 +1823,6 @@
           <t>2024-09-15</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>några få skott</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1842,6 +1832,26 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1858,10 +1868,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119814417</v>
+        <v>119814486</v>
       </c>
       <c r="B12" t="n">
-        <v>79567</v>
+        <v>94323</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1874,45 +1884,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>2813</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 14, Vg</t>
+          <t>Middagsmärket 1:1 pos 15, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432268</v>
+        <v>432226</v>
       </c>
       <c r="R12" t="n">
-        <v>6427731</v>
+        <v>6427752</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1947,6 +1950,11 @@
           <t>2024-09-15</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>några få skott</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1956,26 +1964,6 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1992,10 +1980,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119814579</v>
+        <v>119814155</v>
       </c>
       <c r="B13" t="n">
-        <v>79511</v>
+        <v>79567</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2008,37 +1996,45 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 16, Vg</t>
+          <t>Middagsmärket 1:1 pos 13, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432354</v>
+        <v>432326</v>
       </c>
       <c r="R13" t="n">
-        <v>6427857</v>
+        <v>6427828</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2118,7 +2114,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119814155</v>
+        <v>119814417</v>
       </c>
       <c r="B14" t="n">
         <v>79567</v>
@@ -2153,26 +2149,26 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 13, Vg</t>
+          <t>Middagsmärket 1:1 pos 14, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432326</v>
+        <v>432268</v>
       </c>
       <c r="R14" t="n">
-        <v>6427828</v>
+        <v>6427731</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119803900</v>
+        <v>119803848</v>
       </c>
       <c r="B2" t="n">
-        <v>79652</v>
+        <v>94195</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229504</v>
+        <v>2755</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Skuggsprötmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Eurhynchium striatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 8, Vg</t>
+          <t>Middagsmärket 1:1 pos 7, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>431942</v>
+        <v>431908</v>
       </c>
       <c r="R2" t="n">
-        <v>6427740</v>
+        <v>6427794</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,26 +766,6 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -801,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119783315</v>
+        <v>119803920</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1026</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -840,14 +821,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 6, Vg</t>
+          <t>Middagsmärket 1:1 pos 9, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432336</v>
+        <v>431951</v>
       </c>
       <c r="R3" t="n">
-        <v>6427848</v>
+        <v>6427754</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -888,22 +869,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>skogsek (aggregat)</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Quercus robur agg.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -913,7 +890,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Quercus robur agg.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -931,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119783430</v>
+        <v>119803994</v>
       </c>
       <c r="B4" t="n">
-        <v>79607</v>
+        <v>79567</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,25 +920,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -970,14 +947,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 3, Vg</t>
+          <t>Middagsmärket 1:1 pos 10, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432303</v>
+        <v>432217</v>
       </c>
       <c r="R4" t="n">
-        <v>6427851</v>
+        <v>6427776</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1037,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119803848</v>
+        <v>119803900</v>
       </c>
       <c r="B5" t="n">
-        <v>94195</v>
+        <v>79652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,42 +1026,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2755</v>
+        <v>229504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skuggsprötmossa</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eurhynchium striatum</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 7, Vg</t>
+          <t>Middagsmärket 1:1 pos 8, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>431908</v>
+        <v>431942</v>
       </c>
       <c r="R5" t="n">
-        <v>6427794</v>
+        <v>6427740</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1128,6 +1104,26 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1144,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119783586</v>
+        <v>119783553</v>
       </c>
       <c r="B6" t="n">
-        <v>79511</v>
+        <v>79035</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,35 +1152,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>1026</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1278,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119803994</v>
+        <v>119783544</v>
       </c>
       <c r="B7" t="n">
-        <v>79567</v>
+        <v>79607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,25 +1286,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1317,14 +1313,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 10, Vg</t>
+          <t>Middagsmärket 1:1 pos 5, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>432217</v>
+        <v>432321</v>
       </c>
       <c r="R7" t="n">
-        <v>6427776</v>
+        <v>6427859</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1368,6 +1364,26 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1384,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119783475</v>
+        <v>119783430</v>
       </c>
       <c r="B8" t="n">
-        <v>79567</v>
+        <v>79607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1396,25 +1412,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1423,14 +1439,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos4, Vg</t>
+          <t>Middagsmärket 1:1 pos 3, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>432309</v>
+        <v>432303</v>
       </c>
       <c r="R8" t="n">
-        <v>6427862</v>
+        <v>6427851</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1490,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119803920</v>
+        <v>119783586</v>
       </c>
       <c r="B9" t="n">
-        <v>79607</v>
+        <v>79511</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1502,41 +1518,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 9, Vg</t>
+          <t>Middagsmärket 1:1 pos 6, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>431951</v>
+        <v>432336</v>
       </c>
       <c r="R9" t="n">
-        <v>6427754</v>
+        <v>6427848</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1583,12 +1607,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>skogsek (aggregat)</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Quercus robur agg.</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1598,7 +1622,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Quercus robur agg.</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1616,10 +1640,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119783544</v>
+        <v>119783475</v>
       </c>
       <c r="B10" t="n">
-        <v>79607</v>
+        <v>79567</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,25 +1652,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1655,14 +1679,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 5, Vg</t>
+          <t>Middagsmärket 1:1 pos4, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432321</v>
+        <v>432309</v>
       </c>
       <c r="R10" t="n">
-        <v>6427859</v>
+        <v>6427862</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1706,26 +1730,6 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1742,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119814579</v>
+        <v>119814486</v>
       </c>
       <c r="B11" t="n">
-        <v>79511</v>
+        <v>94323</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,37 +1762,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>2813</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 16, Vg</t>
+          <t>Middagsmärket 1:1 pos 15, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>432354</v>
+        <v>432226</v>
       </c>
       <c r="R11" t="n">
-        <v>6427857</v>
+        <v>6427752</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1823,6 +1828,11 @@
           <t>2024-09-15</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>några få skott</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1832,26 +1842,6 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1868,10 +1858,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119814486</v>
+        <v>119814155</v>
       </c>
       <c r="B12" t="n">
-        <v>94323</v>
+        <v>79567</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1884,38 +1874,45 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2813</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 15, Vg</t>
+          <t>Middagsmärket 1:1 pos 13, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432226</v>
+        <v>432326</v>
       </c>
       <c r="R12" t="n">
-        <v>6427752</v>
+        <v>6427828</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1950,11 +1947,6 @@
           <t>2024-09-15</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>några få skott</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1964,6 +1956,26 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1980,10 +1992,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119814155</v>
+        <v>119814579</v>
       </c>
       <c r="B13" t="n">
-        <v>79567</v>
+        <v>79511</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1996,45 +2008,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 13, Vg</t>
+          <t>Middagsmärket 1:1 pos 16, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432326</v>
+        <v>432354</v>
       </c>
       <c r="R13" t="n">
-        <v>6427828</v>
+        <v>6427857</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119803848</v>
+        <v>119783553</v>
       </c>
       <c r="B2" t="n">
-        <v>94195</v>
+        <v>79035</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2755</v>
+        <v>1026</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skuggsprötmossa</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eurhynchium striatum</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 7, Vg</t>
+          <t>Middagsmärket 1:1 pos 6, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>431908</v>
+        <v>432336</v>
       </c>
       <c r="R2" t="n">
-        <v>6427794</v>
+        <v>6427848</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -766,6 +773,26 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119803920</v>
+        <v>119803900</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>79652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +825,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>229504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,14 +848,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 9, Vg</t>
+          <t>Middagsmärket 1:1 pos 8, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>431951</v>
+        <v>431942</v>
       </c>
       <c r="R3" t="n">
-        <v>6427754</v>
+        <v>6427740</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -875,12 +902,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>skogsek (aggregat)</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Quercus robur agg.</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -890,7 +917,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Quercus robur agg.</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -908,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119803994</v>
+        <v>119803848</v>
       </c>
       <c r="B4" t="n">
-        <v>79567</v>
+        <v>94195</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,37 +951,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>2755</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skuggsprötmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Eurhynchium striatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 10, Vg</t>
+          <t>Middagsmärket 1:1 pos 7, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432217</v>
+        <v>431908</v>
       </c>
       <c r="R4" t="n">
-        <v>6427776</v>
+        <v>6427794</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1014,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119803900</v>
+        <v>119783475</v>
       </c>
       <c r="B5" t="n">
-        <v>79652</v>
+        <v>79567</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,25 +1054,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229504</v>
+        <v>229497</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1053,14 +1081,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 8, Vg</t>
+          <t>Middagsmärket 1:1 pos4, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>431942</v>
+        <v>432309</v>
       </c>
       <c r="R5" t="n">
-        <v>6427740</v>
+        <v>6427862</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,26 +1132,6 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1140,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119783553</v>
+        <v>119803920</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,49 +1160,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1026</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 6, Vg</t>
+          <t>Middagsmärket 1:1 pos 9, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432336</v>
+        <v>431951</v>
       </c>
       <c r="R6" t="n">
-        <v>6427848</v>
+        <v>6427754</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>skogsek (aggregat)</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Quercus robur agg.</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Quercus robur agg.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1400,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119783430</v>
+        <v>119803994</v>
       </c>
       <c r="B8" t="n">
-        <v>79607</v>
+        <v>79567</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,25 +1412,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1439,14 +1439,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 3, Vg</t>
+          <t>Middagsmärket 1:1 pos 10, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>432303</v>
+        <v>432217</v>
       </c>
       <c r="R8" t="n">
-        <v>6427851</v>
+        <v>6427776</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119783475</v>
+        <v>119783430</v>
       </c>
       <c r="B10" t="n">
-        <v>79567</v>
+        <v>79607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1652,25 +1652,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1679,14 +1679,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos4, Vg</t>
+          <t>Middagsmärket 1:1 pos 3, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432309</v>
+        <v>432303</v>
       </c>
       <c r="R10" t="n">
-        <v>6427862</v>
+        <v>6427851</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119814486</v>
+        <v>119814155</v>
       </c>
       <c r="B11" t="n">
-        <v>94323</v>
+        <v>79567</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1762,38 +1762,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2813</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 15, Vg</t>
+          <t>Middagsmärket 1:1 pos 13, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>432226</v>
+        <v>432326</v>
       </c>
       <c r="R11" t="n">
-        <v>6427752</v>
+        <v>6427828</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1828,11 +1835,6 @@
           <t>2024-09-15</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>några få skott</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1842,6 +1844,26 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1858,10 +1880,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119814155</v>
+        <v>119814579</v>
       </c>
       <c r="B12" t="n">
-        <v>79567</v>
+        <v>79511</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1874,45 +1896,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 13, Vg</t>
+          <t>Middagsmärket 1:1 pos 16, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432326</v>
+        <v>432354</v>
       </c>
       <c r="R12" t="n">
-        <v>6427828</v>
+        <v>6427857</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1992,10 +2006,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119814579</v>
+        <v>119814486</v>
       </c>
       <c r="B13" t="n">
-        <v>79511</v>
+        <v>94323</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2008,37 +2022,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>2813</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 16, Vg</t>
+          <t>Middagsmärket 1:1 pos 15, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432354</v>
+        <v>432226</v>
       </c>
       <c r="R13" t="n">
-        <v>6427857</v>
+        <v>6427752</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2073,6 +2088,11 @@
           <t>2024-09-15</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>några få skott</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2082,26 +2102,6 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -1400,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119803994</v>
+        <v>119783586</v>
       </c>
       <c r="B8" t="n">
-        <v>79567</v>
+        <v>79511</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1416,37 +1416,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 10, Vg</t>
+          <t>Middagsmärket 1:1 pos 6, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>432217</v>
+        <v>432336</v>
       </c>
       <c r="R8" t="n">
-        <v>6427776</v>
+        <v>6427848</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1490,6 +1498,26 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1506,10 +1534,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119783586</v>
+        <v>119803994</v>
       </c>
       <c r="B9" t="n">
-        <v>79511</v>
+        <v>79567</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1522,45 +1550,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 6, Vg</t>
+          <t>Middagsmärket 1:1 pos 10, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>432336</v>
+        <v>432217</v>
       </c>
       <c r="R9" t="n">
-        <v>6427848</v>
+        <v>6427776</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1604,26 +1624,6 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119783553</v>
+        <v>119783544</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1026</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 6, Vg</t>
+          <t>Middagsmärket 1:1 pos 5, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432336</v>
+        <v>432321</v>
       </c>
       <c r="R2" t="n">
-        <v>6427848</v>
+        <v>6427859</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -809,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119803900</v>
+        <v>119783475</v>
       </c>
       <c r="B3" t="n">
-        <v>79652</v>
+        <v>79583</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,25 +813,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229504</v>
+        <v>229497</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -848,14 +840,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 8, Vg</t>
+          <t>Middagsmärket 1:1 pos4, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>431942</v>
+        <v>432309</v>
       </c>
       <c r="R3" t="n">
-        <v>6427740</v>
+        <v>6427862</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -899,26 +891,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -935,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119803848</v>
+        <v>119803900</v>
       </c>
       <c r="B4" t="n">
-        <v>94195</v>
+        <v>79668</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,42 +919,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2755</v>
+        <v>229504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skuggsprötmossa</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eurhynchium striatum</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 7, Vg</t>
+          <t>Middagsmärket 1:1 pos 8, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>431908</v>
+        <v>431942</v>
       </c>
       <c r="R4" t="n">
-        <v>6427794</v>
+        <v>6427740</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1026,6 +997,26 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1042,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119783475</v>
+        <v>119783553</v>
       </c>
       <c r="B5" t="n">
-        <v>79567</v>
+        <v>79051</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,41 +1045,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>1026</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos4, Vg</t>
+          <t>Middagsmärket 1:1 pos 6, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432309</v>
+        <v>432336</v>
       </c>
       <c r="R5" t="n">
-        <v>6427862</v>
+        <v>6427848</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1132,6 +1131,26 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1148,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119803920</v>
+        <v>119783586</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
+        <v>79527</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,41 +1179,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 9, Vg</t>
+          <t>Middagsmärket 1:1 pos 6, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>431951</v>
+        <v>432336</v>
       </c>
       <c r="R6" t="n">
-        <v>6427754</v>
+        <v>6427848</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1241,12 +1268,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>skogsek (aggregat)</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Quercus robur agg.</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1256,7 +1283,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Quercus robur agg.</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1274,10 +1301,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119783544</v>
+        <v>119803848</v>
       </c>
       <c r="B7" t="n">
-        <v>79607</v>
+        <v>94218</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,41 +1313,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>2755</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggsprötmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Eurhynchium striatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 5, Vg</t>
+          <t>Middagsmärket 1:1 pos 7, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>432321</v>
+        <v>431908</v>
       </c>
       <c r="R7" t="n">
-        <v>6427859</v>
+        <v>6427794</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1364,26 +1392,6 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1400,10 +1408,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119783586</v>
+        <v>119783430</v>
       </c>
       <c r="B8" t="n">
-        <v>79511</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,49 +1420,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 6, Vg</t>
+          <t>Middagsmärket 1:1 pos 3, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>432336</v>
+        <v>432303</v>
       </c>
       <c r="R8" t="n">
-        <v>6427848</v>
+        <v>6427851</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1498,26 +1498,6 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1534,10 +1514,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119803994</v>
+        <v>119803920</v>
       </c>
       <c r="B9" t="n">
-        <v>79567</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1546,25 +1526,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1573,14 +1553,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 10, Vg</t>
+          <t>Middagsmärket 1:1 pos 9, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>432217</v>
+        <v>431951</v>
       </c>
       <c r="R9" t="n">
-        <v>6427776</v>
+        <v>6427754</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1624,6 +1604,26 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>skogsek (aggregat)</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Quercus robur agg.</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Quercus robur agg.</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1640,10 +1640,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119783430</v>
+        <v>119803994</v>
       </c>
       <c r="B10" t="n">
-        <v>79607</v>
+        <v>79583</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1652,25 +1652,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1679,14 +1679,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 3, Vg</t>
+          <t>Middagsmärket 1:1 pos 10, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432303</v>
+        <v>432217</v>
       </c>
       <c r="R10" t="n">
-        <v>6427851</v>
+        <v>6427776</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119814155</v>
+        <v>119814579</v>
       </c>
       <c r="B11" t="n">
-        <v>79567</v>
+        <v>79527</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1762,45 +1762,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 13, Vg</t>
+          <t>Middagsmärket 1:1 pos 16, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>432326</v>
+        <v>432354</v>
       </c>
       <c r="R11" t="n">
-        <v>6427828</v>
+        <v>6427857</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1880,10 +1872,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119814579</v>
+        <v>119814417</v>
       </c>
       <c r="B12" t="n">
-        <v>79511</v>
+        <v>79583</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1896,37 +1888,45 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 16, Vg</t>
+          <t>Middagsmärket 1:1 pos 14, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432354</v>
+        <v>432268</v>
       </c>
       <c r="R12" t="n">
-        <v>6427857</v>
+        <v>6427731</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2009,7 +2009,7 @@
         <v>119814486</v>
       </c>
       <c r="B13" t="n">
-        <v>94323</v>
+        <v>94346</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119814417</v>
+        <v>119814155</v>
       </c>
       <c r="B14" t="n">
-        <v>79567</v>
+        <v>79583</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2153,26 +2153,26 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 14, Vg</t>
+          <t>Middagsmärket 1:1 pos 13, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432268</v>
+        <v>432326</v>
       </c>
       <c r="R14" t="n">
-        <v>6427731</v>
+        <v>6427828</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119783544</v>
+        <v>119783553</v>
       </c>
       <c r="B2" t="n">
-        <v>79623</v>
+        <v>79051</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1026</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 5, Vg</t>
+          <t>Middagsmärket 1:1 pos 6, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432321</v>
+        <v>432336</v>
       </c>
       <c r="R2" t="n">
-        <v>6427859</v>
+        <v>6427848</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -801,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119783475</v>
+        <v>119803848</v>
       </c>
       <c r="B3" t="n">
-        <v>79583</v>
+        <v>94218</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,37 +825,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>2755</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skuggsprötmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Eurhynchium striatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos4, Vg</t>
+          <t>Middagsmärket 1:1 pos 7, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432309</v>
+        <v>431908</v>
       </c>
       <c r="R3" t="n">
-        <v>6427862</v>
+        <v>6427794</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1033,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119783553</v>
+        <v>119803994</v>
       </c>
       <c r="B5" t="n">
-        <v>79051</v>
+        <v>79583</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,49 +1054,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1026</v>
+        <v>229497</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 6, Vg</t>
+          <t>Middagsmärket 1:1 pos 10, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432336</v>
+        <v>432217</v>
       </c>
       <c r="R5" t="n">
-        <v>6427848</v>
+        <v>6427776</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1131,26 +1132,6 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1301,10 +1282,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119803848</v>
+        <v>119803920</v>
       </c>
       <c r="B7" t="n">
-        <v>94218</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1313,42 +1294,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2755</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skuggsprötmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Eurhynchium striatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 7, Vg</t>
+          <t>Middagsmärket 1:1 pos 9, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431908</v>
+        <v>431951</v>
       </c>
       <c r="R7" t="n">
-        <v>6427794</v>
+        <v>6427754</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1392,6 +1372,26 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>skogsek (aggregat)</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Quercus robur agg.</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Quercus robur agg.</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1514,10 +1514,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119803920</v>
+        <v>119783475</v>
       </c>
       <c r="B9" t="n">
-        <v>79623</v>
+        <v>79583</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1526,25 +1526,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1553,14 +1553,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 9, Vg</t>
+          <t>Middagsmärket 1:1 pos4, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>431951</v>
+        <v>432309</v>
       </c>
       <c r="R9" t="n">
-        <v>6427754</v>
+        <v>6427862</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1604,26 +1604,6 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>skogsek (aggregat)</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Quercus robur agg.</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Quercus robur agg.</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1640,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119803994</v>
+        <v>119783544</v>
       </c>
       <c r="B10" t="n">
-        <v>79583</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1652,25 +1632,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1679,14 +1659,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 10, Vg</t>
+          <t>Middagsmärket 1:1 pos 5, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432217</v>
+        <v>432321</v>
       </c>
       <c r="R10" t="n">
-        <v>6427776</v>
+        <v>6427859</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1730,6 +1710,26 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1872,7 +1872,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119814417</v>
+        <v>119814155</v>
       </c>
       <c r="B12" t="n">
         <v>79583</v>
@@ -1907,26 +1907,26 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 14, Vg</t>
+          <t>Middagsmärket 1:1 pos 13, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432268</v>
+        <v>432326</v>
       </c>
       <c r="R12" t="n">
-        <v>6427731</v>
+        <v>6427828</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119814155</v>
+        <v>119814417</v>
       </c>
       <c r="B14" t="n">
         <v>79583</v>
@@ -2153,26 +2153,26 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 13, Vg</t>
+          <t>Middagsmärket 1:1 pos 14, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432326</v>
+        <v>432268</v>
       </c>
       <c r="R14" t="n">
-        <v>6427828</v>
+        <v>6427731</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -1746,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119814579</v>
+        <v>119814155</v>
       </c>
       <c r="B11" t="n">
-        <v>79527</v>
+        <v>79583</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1762,37 +1762,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 16, Vg</t>
+          <t>Middagsmärket 1:1 pos 13, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>432354</v>
+        <v>432326</v>
       </c>
       <c r="R11" t="n">
-        <v>6427857</v>
+        <v>6427828</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1872,10 +1880,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119814155</v>
+        <v>119814486</v>
       </c>
       <c r="B12" t="n">
-        <v>79583</v>
+        <v>94346</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1888,45 +1896,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>2813</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 13, Vg</t>
+          <t>Middagsmärket 1:1 pos 15, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432326</v>
+        <v>432226</v>
       </c>
       <c r="R12" t="n">
-        <v>6427828</v>
+        <v>6427752</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1961,6 +1962,11 @@
           <t>2024-09-15</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>några få skott</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1970,26 +1976,6 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2006,10 +1992,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119814486</v>
+        <v>119814417</v>
       </c>
       <c r="B13" t="n">
-        <v>94346</v>
+        <v>79583</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2022,38 +2008,45 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2813</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 15, Vg</t>
+          <t>Middagsmärket 1:1 pos 14, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432226</v>
+        <v>432268</v>
       </c>
       <c r="R13" t="n">
-        <v>6427752</v>
+        <v>6427731</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2088,11 +2081,6 @@
           <t>2024-09-15</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>några få skott</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2102,6 +2090,26 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2118,10 +2126,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119814417</v>
+        <v>119814579</v>
       </c>
       <c r="B14" t="n">
-        <v>79583</v>
+        <v>79527</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2134,45 +2142,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 14, Vg</t>
+          <t>Middagsmärket 1:1 pos 16, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432268</v>
+        <v>432354</v>
       </c>
       <c r="R14" t="n">
-        <v>6427731</v>
+        <v>6427857</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -2255,7 +2255,7 @@
         <v>120967851</v>
       </c>
       <c r="B15" t="n">
-        <v>91302</v>
+        <v>91312</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -2255,7 +2255,7 @@
         <v>120967851</v>
       </c>
       <c r="B15" t="n">
-        <v>91312</v>
+        <v>91324</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2352,6 +2352,615 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124882964</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Middagsmärket 1:1 pos18, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>432235</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6427836</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124882863</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79319</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1026</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ädellav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Megalaria grossa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Middagsmärket 1:1 pos18, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>432235</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6427836</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124883045</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79319</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1026</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ädellav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Megalaria grossa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Middagsmärker 1:1 pos 19, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>432154</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6427796</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124883023</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79851</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Middagsmärket 1:1 pos18, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>432235</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6427836</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På en hasselstam direkt intill den stora aspen med lunglav, ädellav och korallblylav (samma koordinat - se bilder för lunglaven).</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124779232</v>
+      </c>
+      <c r="B20" t="n">
+        <v>95551</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>210</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Smedstorp pos.27, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>431805</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6427767</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -2354,10 +2354,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124882964</v>
+        <v>124779232</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>95551</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2366,41 +2366,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>210</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos18, Vg</t>
+          <t>Smedstorp 1:1 pos54, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432235</v>
+        <v>431805</v>
       </c>
       <c r="R16" t="n">
-        <v>6427836</v>
+        <v>6427767</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2444,21 +2453,6 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2475,10 +2469,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124882863</v>
+        <v>124882917</v>
       </c>
       <c r="B17" t="n">
-        <v>79319</v>
+        <v>79851</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2487,25 +2481,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1026</v>
+        <v>229497</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2722,10 +2716,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124883023</v>
+        <v>124882863</v>
       </c>
       <c r="B19" t="n">
-        <v>79851</v>
+        <v>79319</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2734,25 +2728,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>1026</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2805,7 +2799,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På en hasselstam direkt intill den stora aspen med lunglav, ädellav och korallblylav (samma koordinat - se bilder för lunglaven).</t>
+          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2820,17 +2814,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>hassel</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Corylus avellana</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Corylus avellana</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2848,10 +2842,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124779232</v>
+        <v>124882964</v>
       </c>
       <c r="B20" t="n">
-        <v>95551</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2860,50 +2854,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>210</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Smedstorp pos.27, Vg</t>
+          <t>Middagsmärket 1:1 pos18, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>431805</v>
+        <v>432235</v>
       </c>
       <c r="R20" t="n">
-        <v>6427767</v>
+        <v>6427836</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2947,6 +2932,21 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2961,6 +2961,1071 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>124911723</v>
+      </c>
+      <c r="B21" t="n">
+        <v>74893</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>308</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Middagsmärket 1:1 pos20, Vg</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>432181</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6427847</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>124911842</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79851</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Middagsmärker 1:1 pos22, Vg</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>431972</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6427781</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>124911784</v>
+      </c>
+      <c r="B23" t="n">
+        <v>95335</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Middagsmärket 1:1 pos 21, Vg</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>432143</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6427793</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>124911863</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79936</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Middagsmärket 1:1 pos 123, Vg</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>431964</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6427784</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>124911865</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79190</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Middagsmärket 1:1 pos25, Vg</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>431886</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6427693</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>124911742</v>
+      </c>
+      <c r="B26" t="n">
+        <v>74885</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Middagsmärket 1:1 pos20, Vg</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>432181</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6427847</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>124911802</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79851</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Middagsmärker 1:1 pos 19, Vg</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>432154</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6427796</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>124911788</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79851</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Middagsmärket 1:1 pos 21, Vg</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>432143</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6427793</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>124911853</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79936</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Middagsmärker 1:1 pos22, Vg</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>431972</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6427781</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -2354,10 +2354,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124779232</v>
+        <v>124883023</v>
       </c>
       <c r="B16" t="n">
-        <v>95551</v>
+        <v>79851</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2370,46 +2370,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>210</v>
+        <v>229497</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Smedstorp 1:1 pos54, Vg</t>
+          <t>Middagsmärket 1:1 pos18, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431805</v>
+        <v>432235</v>
       </c>
       <c r="R16" t="n">
-        <v>6427767</v>
+        <v>6427836</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2444,6 +2435,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På en hasselstam direkt intill den stora aspen med lunglav, ädellav och korallblylav (samma koordinat - se bilder för lunglaven).</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2453,6 +2449,21 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2469,10 +2480,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124882917</v>
+        <v>124882964</v>
       </c>
       <c r="B17" t="n">
-        <v>79851</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2481,25 +2492,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2550,11 +2561,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2842,10 +2848,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124882964</v>
+        <v>124779232</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>95551</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2854,41 +2860,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>210</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos18, Vg</t>
+          <t>Smedstorp 1:1 pos54, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>432235</v>
+        <v>431805</v>
       </c>
       <c r="R20" t="n">
-        <v>6427836</v>
+        <v>6427767</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2932,21 +2947,6 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2963,10 +2963,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124911723</v>
+        <v>124911802</v>
       </c>
       <c r="B21" t="n">
-        <v>74893</v>
+        <v>79851</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2975,25 +2975,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3002,14 +3002,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos20, Vg</t>
+          <t>Middagsmärker 1:1 pos 19, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>432181</v>
+        <v>432154</v>
       </c>
       <c r="R21" t="n">
-        <v>6427847</v>
+        <v>6427796</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3056,17 +3056,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3084,10 +3084,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124911842</v>
+        <v>124911742</v>
       </c>
       <c r="B22" t="n">
-        <v>79851</v>
+        <v>74885</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3100,21 +3100,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>6439</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3123,14 +3123,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos22, Vg</t>
+          <t>Middagsmärket 1:1 pos20, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431972</v>
+        <v>432181</v>
       </c>
       <c r="R22" t="n">
-        <v>6427781</v>
+        <v>6427847</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3174,21 +3174,6 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3205,10 +3190,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124911784</v>
+        <v>124911863</v>
       </c>
       <c r="B23" t="n">
-        <v>95335</v>
+        <v>79936</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3217,42 +3202,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2809</v>
+        <v>229504</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 21, Vg</t>
+          <t>Middagsmärket 1:1 pos 123, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>432143</v>
+        <v>431964</v>
       </c>
       <c r="R23" t="n">
-        <v>6427793</v>
+        <v>6427784</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3287,11 +3271,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3301,6 +3280,21 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3317,10 +3311,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124911863</v>
+        <v>124911784</v>
       </c>
       <c r="B24" t="n">
-        <v>79936</v>
+        <v>95335</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3329,41 +3323,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229504</v>
+        <v>2809</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 123, Vg</t>
+          <t>Middagsmärket 1:1 pos 21, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>431964</v>
+        <v>432143</v>
       </c>
       <c r="R24" t="n">
-        <v>6427784</v>
+        <v>6427793</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3398,6 +3393,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3407,21 +3407,6 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3438,10 +3423,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124911865</v>
+        <v>124911853</v>
       </c>
       <c r="B25" t="n">
-        <v>79190</v>
+        <v>79936</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3450,25 +3435,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6431</v>
+        <v>229504</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3477,14 +3462,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos25, Vg</t>
+          <t>Middagsmärker 1:1 pos22, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>431886</v>
+        <v>431972</v>
       </c>
       <c r="R25" t="n">
-        <v>6427693</v>
+        <v>6427781</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3531,17 +3516,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3559,10 +3544,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124911742</v>
+        <v>124911865</v>
       </c>
       <c r="B26" t="n">
-        <v>74885</v>
+        <v>79190</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3575,21 +3560,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6439</v>
+        <v>6431</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3598,14 +3583,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos20, Vg</t>
+          <t>Middagsmärket 1:1 pos25, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>432181</v>
+        <v>431886</v>
       </c>
       <c r="R26" t="n">
-        <v>6427847</v>
+        <v>6427693</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3649,6 +3634,21 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3665,7 +3665,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124911802</v>
+        <v>124911788</v>
       </c>
       <c r="B27" t="n">
         <v>79851</v>
@@ -3704,14 +3704,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos 19, Vg</t>
+          <t>Middagsmärket 1:1 pos 21, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>432154</v>
+        <v>432143</v>
       </c>
       <c r="R27" t="n">
-        <v>6427796</v>
+        <v>6427793</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3786,7 +3786,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124911788</v>
+        <v>124911842</v>
       </c>
       <c r="B28" t="n">
         <v>79851</v>
@@ -3825,14 +3825,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 21, Vg</t>
+          <t>Middagsmärker 1:1 pos22, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>432143</v>
+        <v>431972</v>
       </c>
       <c r="R28" t="n">
-        <v>6427793</v>
+        <v>6427781</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3879,17 +3879,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3907,10 +3907,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124911853</v>
+        <v>124911723</v>
       </c>
       <c r="B29" t="n">
-        <v>79936</v>
+        <v>74893</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3923,21 +3923,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229504</v>
+        <v>308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3946,14 +3946,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos22, Vg</t>
+          <t>Middagsmärket 1:1 pos20, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>431972</v>
+        <v>432181</v>
       </c>
       <c r="R29" t="n">
-        <v>6427781</v>
+        <v>6427847</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4000,17 +4000,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -2354,10 +2354,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124883023</v>
+        <v>124779232</v>
       </c>
       <c r="B16" t="n">
-        <v>79851</v>
+        <v>95551</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2370,37 +2370,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos18, Vg</t>
+          <t>Smedstorp 1:1 pos54, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432235</v>
+        <v>431805</v>
       </c>
       <c r="R16" t="n">
-        <v>6427836</v>
+        <v>6427767</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2435,11 +2444,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På en hasselstam direkt intill den stora aspen med lunglav, ädellav och korallblylav (samma koordinat - se bilder för lunglaven).</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2449,21 +2453,6 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>hassel</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2480,10 +2469,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124882964</v>
+        <v>124882917</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>79851</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2492,25 +2481,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2561,6 +2550,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2601,7 +2595,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124883045</v>
+        <v>124882863</v>
       </c>
       <c r="B18" t="n">
         <v>79319</v>
@@ -2640,14 +2634,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos 19, Vg</t>
+          <t>Middagsmärket 1:1 pos18, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>432154</v>
+        <v>432235</v>
       </c>
       <c r="R18" t="n">
-        <v>6427796</v>
+        <v>6427836</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2680,6 +2674,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2722,10 +2721,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124882863</v>
+        <v>124882964</v>
       </c>
       <c r="B19" t="n">
-        <v>79319</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2734,25 +2733,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1026</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2803,11 +2802,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2848,10 +2842,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124779232</v>
+        <v>124883045</v>
       </c>
       <c r="B20" t="n">
-        <v>95551</v>
+        <v>79319</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2860,50 +2854,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>210</v>
+        <v>1026</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Smedstorp 1:1 pos54, Vg</t>
+          <t>Middagsmärker 1:1 pos 19, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>431805</v>
+        <v>432154</v>
       </c>
       <c r="R20" t="n">
-        <v>6427767</v>
+        <v>6427796</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2947,6 +2932,21 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2963,10 +2963,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124911802</v>
+        <v>124911723</v>
       </c>
       <c r="B21" t="n">
-        <v>79851</v>
+        <v>74893</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2975,25 +2975,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3002,14 +3002,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos 19, Vg</t>
+          <t>Middagsmärket 1:1 pos20, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>432154</v>
+        <v>432181</v>
       </c>
       <c r="R21" t="n">
-        <v>6427796</v>
+        <v>6427847</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3056,17 +3056,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3084,10 +3084,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124911742</v>
+        <v>124911865</v>
       </c>
       <c r="B22" t="n">
-        <v>74885</v>
+        <v>79190</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3100,21 +3100,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6439</v>
+        <v>6431</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3123,14 +3123,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos20, Vg</t>
+          <t>Middagsmärket 1:1 pos25, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>432181</v>
+        <v>431886</v>
       </c>
       <c r="R22" t="n">
-        <v>6427847</v>
+        <v>6427693</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3174,6 +3174,21 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3190,10 +3205,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124911863</v>
+        <v>124911802</v>
       </c>
       <c r="B23" t="n">
-        <v>79936</v>
+        <v>79851</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3202,25 +3217,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229504</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3229,14 +3244,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 123, Vg</t>
+          <t>Middagsmärker 1:1 pos 19, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431964</v>
+        <v>432154</v>
       </c>
       <c r="R23" t="n">
-        <v>6427784</v>
+        <v>6427796</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3283,17 +3298,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3311,10 +3326,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124911784</v>
+        <v>124911742</v>
       </c>
       <c r="B24" t="n">
-        <v>95335</v>
+        <v>74885</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3327,38 +3342,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2809</v>
+        <v>6439</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 21, Vg</t>
+          <t>Middagsmärket 1:1 pos20, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>432143</v>
+        <v>432181</v>
       </c>
       <c r="R24" t="n">
-        <v>6427793</v>
+        <v>6427847</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3391,11 +3405,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3544,10 +3553,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124911865</v>
+        <v>124911863</v>
       </c>
       <c r="B26" t="n">
-        <v>79190</v>
+        <v>79936</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3556,25 +3565,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6431</v>
+        <v>229504</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3583,14 +3592,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos25, Vg</t>
+          <t>Middagsmärket 1:1 pos 123, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>431886</v>
+        <v>431964</v>
       </c>
       <c r="R26" t="n">
-        <v>6427693</v>
+        <v>6427784</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3637,17 +3646,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3665,7 +3674,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124911788</v>
+        <v>124911842</v>
       </c>
       <c r="B27" t="n">
         <v>79851</v>
@@ -3704,14 +3713,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 21, Vg</t>
+          <t>Middagsmärker 1:1 pos22, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>432143</v>
+        <v>431972</v>
       </c>
       <c r="R27" t="n">
-        <v>6427793</v>
+        <v>6427781</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3758,17 +3767,17 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3786,10 +3795,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124911842</v>
+        <v>124911784</v>
       </c>
       <c r="B28" t="n">
-        <v>79851</v>
+        <v>95335</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3802,37 +3811,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229497</v>
+        <v>2809</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos22, Vg</t>
+          <t>Middagsmärket 1:1 pos 21, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>431972</v>
+        <v>432143</v>
       </c>
       <c r="R28" t="n">
-        <v>6427781</v>
+        <v>6427793</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3867,6 +3877,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3876,21 +3891,6 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3907,10 +3907,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124911723</v>
+        <v>124911788</v>
       </c>
       <c r="B29" t="n">
-        <v>74893</v>
+        <v>79851</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3919,25 +3919,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>308</v>
+        <v>229497</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3946,14 +3946,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos20, Vg</t>
+          <t>Middagsmärket 1:1 pos 21, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>432181</v>
+        <v>432143</v>
       </c>
       <c r="R29" t="n">
-        <v>6427847</v>
+        <v>6427793</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4000,17 +4000,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -2595,10 +2595,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124882863</v>
+        <v>124882964</v>
       </c>
       <c r="B18" t="n">
-        <v>79319</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2607,25 +2607,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1026</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2676,11 +2676,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2721,10 +2716,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124882964</v>
+        <v>124882863</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>79319</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2733,25 +2728,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1026</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2800,6 +2795,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -2354,10 +2354,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124779232</v>
+        <v>124882917</v>
       </c>
       <c r="B16" t="n">
-        <v>95551</v>
+        <v>79851</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2370,46 +2370,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>210</v>
+        <v>229497</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Smedstorp 1:1 pos54, Vg</t>
+          <t>Middagsmärket 1:1 pos18, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431805</v>
+        <v>432235</v>
       </c>
       <c r="R16" t="n">
-        <v>6427767</v>
+        <v>6427836</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2444,6 +2435,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2453,6 +2449,21 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2469,10 +2480,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124882917</v>
+        <v>124882964</v>
       </c>
       <c r="B17" t="n">
-        <v>79851</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2481,25 +2492,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2550,11 +2561,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2595,10 +2601,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124882964</v>
+        <v>124883045</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>79319</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2607,25 +2613,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1026</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2634,14 +2640,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos18, Vg</t>
+          <t>Middagsmärker 1:1 pos 19, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>432235</v>
+        <v>432154</v>
       </c>
       <c r="R18" t="n">
-        <v>6427836</v>
+        <v>6427796</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2716,10 +2722,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124882863</v>
+        <v>124779232</v>
       </c>
       <c r="B19" t="n">
-        <v>79319</v>
+        <v>95551</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2728,41 +2734,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1026</v>
+        <v>210</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos18, Vg</t>
+          <t>Smedstorp 1:1 pos54, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432235</v>
+        <v>431805</v>
       </c>
       <c r="R19" t="n">
-        <v>6427836</v>
+        <v>6427767</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2797,11 +2812,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2811,21 +2821,6 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2842,7 +2837,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124883045</v>
+        <v>124882863</v>
       </c>
       <c r="B20" t="n">
         <v>79319</v>
@@ -2881,14 +2876,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos 19, Vg</t>
+          <t>Middagsmärket 1:1 pos18, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>432154</v>
+        <v>432235</v>
       </c>
       <c r="R20" t="n">
-        <v>6427796</v>
+        <v>6427836</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2921,6 +2916,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3084,10 +3084,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124911865</v>
+        <v>124911853</v>
       </c>
       <c r="B22" t="n">
-        <v>79190</v>
+        <v>79936</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3096,25 +3096,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6431</v>
+        <v>229504</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3123,14 +3123,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos25, Vg</t>
+          <t>Middagsmärker 1:1 pos22, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431886</v>
+        <v>431972</v>
       </c>
       <c r="R22" t="n">
-        <v>6427693</v>
+        <v>6427781</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3177,17 +3177,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3205,10 +3205,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124911802</v>
+        <v>124911865</v>
       </c>
       <c r="B23" t="n">
-        <v>79851</v>
+        <v>79190</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3221,21 +3221,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>6431</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3244,14 +3244,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos 19, Vg</t>
+          <t>Middagsmärket 1:1 pos25, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>432154</v>
+        <v>431886</v>
       </c>
       <c r="R23" t="n">
-        <v>6427796</v>
+        <v>6427693</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3326,10 +3326,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124911742</v>
+        <v>124911788</v>
       </c>
       <c r="B24" t="n">
-        <v>74885</v>
+        <v>79851</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3342,21 +3342,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6439</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3365,14 +3365,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos20, Vg</t>
+          <t>Middagsmärket 1:1 pos 21, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>432181</v>
+        <v>432143</v>
       </c>
       <c r="R24" t="n">
-        <v>6427847</v>
+        <v>6427793</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3416,6 +3416,21 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3432,10 +3447,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124911853</v>
+        <v>124911842</v>
       </c>
       <c r="B25" t="n">
-        <v>79936</v>
+        <v>79851</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3444,25 +3459,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229504</v>
+        <v>229497</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3553,10 +3568,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124911863</v>
+        <v>124911784</v>
       </c>
       <c r="B26" t="n">
-        <v>79936</v>
+        <v>95335</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3565,41 +3580,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229504</v>
+        <v>2809</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 123, Vg</t>
+          <t>Middagsmärket 1:1 pos 21, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>431964</v>
+        <v>432143</v>
       </c>
       <c r="R26" t="n">
-        <v>6427784</v>
+        <v>6427793</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3634,6 +3650,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3643,21 +3664,6 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3674,10 +3680,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124911842</v>
+        <v>124911742</v>
       </c>
       <c r="B27" t="n">
-        <v>79851</v>
+        <v>74885</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3690,21 +3696,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229497</v>
+        <v>6439</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3713,14 +3719,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos22, Vg</t>
+          <t>Middagsmärket 1:1 pos20, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>431972</v>
+        <v>432181</v>
       </c>
       <c r="R27" t="n">
-        <v>6427781</v>
+        <v>6427847</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3764,21 +3770,6 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3795,10 +3786,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124911784</v>
+        <v>124911863</v>
       </c>
       <c r="B28" t="n">
-        <v>95335</v>
+        <v>79936</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3807,42 +3798,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2809</v>
+        <v>229504</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 21, Vg</t>
+          <t>Middagsmärket 1:1 pos 123, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>432143</v>
+        <v>431964</v>
       </c>
       <c r="R28" t="n">
-        <v>6427793</v>
+        <v>6427784</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3877,11 +3867,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3891,6 +3876,21 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3907,7 +3907,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124911788</v>
+        <v>124911802</v>
       </c>
       <c r="B29" t="n">
         <v>79851</v>
@@ -3946,14 +3946,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 21, Vg</t>
+          <t>Middagsmärker 1:1 pos 19, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>432143</v>
+        <v>432154</v>
       </c>
       <c r="R29" t="n">
-        <v>6427793</v>
+        <v>6427796</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -2354,10 +2354,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124882917</v>
+        <v>124882863</v>
       </c>
       <c r="B16" t="n">
-        <v>79851</v>
+        <v>79319</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2366,25 +2366,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>1026</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124882964</v>
+        <v>124883023</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>79851</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2492,25 +2492,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2561,6 +2561,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På en hasselstam direkt intill den stora aspen med lunglav, ädellav och korallblylav (samma koordinat - se bilder för lunglaven).</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2573,17 +2578,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>hassel</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Corylus avellana</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Corylus avellana</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2722,10 +2727,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124779232</v>
+        <v>124882964</v>
       </c>
       <c r="B19" t="n">
-        <v>95551</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2734,50 +2739,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>210</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Smedstorp 1:1 pos54, Vg</t>
+          <t>Middagsmärket 1:1 pos18, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>431805</v>
+        <v>432235</v>
       </c>
       <c r="R19" t="n">
-        <v>6427767</v>
+        <v>6427836</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2821,6 +2817,21 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2837,10 +2848,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124882863</v>
+        <v>124779232</v>
       </c>
       <c r="B20" t="n">
-        <v>79319</v>
+        <v>95551</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2849,41 +2860,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1026</v>
+        <v>210</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos18, Vg</t>
+          <t>Smedstorp 1:1 pos54, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>432235</v>
+        <v>431805</v>
       </c>
       <c r="R20" t="n">
-        <v>6427836</v>
+        <v>6427767</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2918,11 +2938,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2932,21 +2947,6 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2963,10 +2963,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124911723</v>
+        <v>124911865</v>
       </c>
       <c r="B21" t="n">
-        <v>74893</v>
+        <v>79190</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2975,25 +2975,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>6431</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3002,14 +3002,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos20, Vg</t>
+          <t>Middagsmärket 1:1 pos25, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>432181</v>
+        <v>431886</v>
       </c>
       <c r="R21" t="n">
-        <v>6427847</v>
+        <v>6427693</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3056,17 +3056,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3084,10 +3084,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124911853</v>
+        <v>124911802</v>
       </c>
       <c r="B22" t="n">
-        <v>79936</v>
+        <v>79851</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3096,25 +3096,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229504</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3123,14 +3123,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos22, Vg</t>
+          <t>Middagsmärker 1:1 pos 19, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431972</v>
+        <v>432154</v>
       </c>
       <c r="R22" t="n">
-        <v>6427781</v>
+        <v>6427796</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3177,17 +3177,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3205,10 +3205,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124911865</v>
+        <v>124911853</v>
       </c>
       <c r="B23" t="n">
-        <v>79190</v>
+        <v>79936</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3217,25 +3217,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6431</v>
+        <v>229504</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3244,14 +3244,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos25, Vg</t>
+          <t>Middagsmärker 1:1 pos22, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431886</v>
+        <v>431972</v>
       </c>
       <c r="R23" t="n">
-        <v>6427693</v>
+        <v>6427781</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3298,17 +3298,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124911842</v>
+        <v>124911742</v>
       </c>
       <c r="B25" t="n">
-        <v>79851</v>
+        <v>74885</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3463,21 +3463,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>6439</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3486,14 +3486,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos22, Vg</t>
+          <t>Middagsmärket 1:1 pos20, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>431972</v>
+        <v>432181</v>
       </c>
       <c r="R25" t="n">
-        <v>6427781</v>
+        <v>6427847</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3537,21 +3537,6 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3568,10 +3553,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124911784</v>
+        <v>124911723</v>
       </c>
       <c r="B26" t="n">
-        <v>95335</v>
+        <v>74893</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3580,42 +3565,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2809</v>
+        <v>308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 21, Vg</t>
+          <t>Middagsmärket 1:1 pos20, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>432143</v>
+        <v>432181</v>
       </c>
       <c r="R26" t="n">
-        <v>6427793</v>
+        <v>6427847</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3650,11 +3634,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3664,6 +3643,21 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3680,10 +3674,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124911742</v>
+        <v>124911784</v>
       </c>
       <c r="B27" t="n">
-        <v>74885</v>
+        <v>95335</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3696,37 +3690,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6439</v>
+        <v>2809</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos20, Vg</t>
+          <t>Middagsmärket 1:1 pos 21, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>432181</v>
+        <v>432143</v>
       </c>
       <c r="R27" t="n">
-        <v>6427847</v>
+        <v>6427793</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3759,6 +3754,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3786,10 +3786,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124911863</v>
+        <v>124911842</v>
       </c>
       <c r="B28" t="n">
-        <v>79936</v>
+        <v>79851</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3798,25 +3798,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229504</v>
+        <v>229497</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3825,14 +3825,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 123, Vg</t>
+          <t>Middagsmärker 1:1 pos22, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>431964</v>
+        <v>431972</v>
       </c>
       <c r="R28" t="n">
-        <v>6427784</v>
+        <v>6427781</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3907,10 +3907,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124911802</v>
+        <v>124911863</v>
       </c>
       <c r="B29" t="n">
-        <v>79851</v>
+        <v>79936</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3919,25 +3919,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>229504</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3946,14 +3946,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos 19, Vg</t>
+          <t>Middagsmärket 1:1 pos 123, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>432154</v>
+        <v>431964</v>
       </c>
       <c r="R29" t="n">
-        <v>6427796</v>
+        <v>6427784</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4000,17 +4000,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -2354,10 +2354,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124882863</v>
+        <v>124883023</v>
       </c>
       <c r="B16" t="n">
-        <v>79319</v>
+        <v>79851</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2366,25 +2366,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1026</v>
+        <v>229497</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
+          <t>På en hasselstam direkt intill den stora aspen med lunglav, ädellav och korallblylav (samma koordinat - se bilder för lunglaven).</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2452,17 +2452,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>hassel</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Corylus avellana</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Corylus avellana</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124883023</v>
+        <v>124779232</v>
       </c>
       <c r="B17" t="n">
-        <v>79851</v>
+        <v>95551</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2496,37 +2496,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos18, Vg</t>
+          <t>Smedstorp 1:1 pos54, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432235</v>
+        <v>431805</v>
       </c>
       <c r="R17" t="n">
-        <v>6427836</v>
+        <v>6427767</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2561,11 +2570,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På en hasselstam direkt intill den stora aspen med lunglav, ädellav och korallblylav (samma koordinat - se bilder för lunglaven).</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2575,21 +2579,6 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>hassel</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2727,10 +2716,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124882964</v>
+        <v>124882863</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>79319</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2739,25 +2728,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1026</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2808,6 +2797,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2848,10 +2842,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124779232</v>
+        <v>124882964</v>
       </c>
       <c r="B20" t="n">
-        <v>95551</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2860,50 +2854,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>210</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Smedstorp 1:1 pos54, Vg</t>
+          <t>Middagsmärket 1:1 pos18, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>431805</v>
+        <v>432235</v>
       </c>
       <c r="R20" t="n">
-        <v>6427767</v>
+        <v>6427836</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2947,6 +2932,21 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2963,10 +2963,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124911865</v>
+        <v>124911853</v>
       </c>
       <c r="B21" t="n">
-        <v>79190</v>
+        <v>79936</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2975,25 +2975,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6431</v>
+        <v>229504</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3002,14 +3002,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos25, Vg</t>
+          <t>Middagsmärker 1:1 pos22, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>431886</v>
+        <v>431972</v>
       </c>
       <c r="R21" t="n">
-        <v>6427693</v>
+        <v>6427781</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3056,17 +3056,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3084,7 +3084,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124911802</v>
+        <v>124911788</v>
       </c>
       <c r="B22" t="n">
         <v>79851</v>
@@ -3123,14 +3123,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos 19, Vg</t>
+          <t>Middagsmärket 1:1 pos 21, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>432154</v>
+        <v>432143</v>
       </c>
       <c r="R22" t="n">
-        <v>6427796</v>
+        <v>6427793</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3205,7 +3205,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124911853</v>
+        <v>124911863</v>
       </c>
       <c r="B23" t="n">
         <v>79936</v>
@@ -3244,14 +3244,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos22, Vg</t>
+          <t>Middagsmärket 1:1 pos 123, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431972</v>
+        <v>431964</v>
       </c>
       <c r="R23" t="n">
-        <v>6427781</v>
+        <v>6427784</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3326,10 +3326,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124911788</v>
+        <v>124911865</v>
       </c>
       <c r="B24" t="n">
-        <v>79851</v>
+        <v>79190</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3342,21 +3342,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>6431</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3365,14 +3365,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 21, Vg</t>
+          <t>Middagsmärket 1:1 pos25, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>432143</v>
+        <v>431886</v>
       </c>
       <c r="R24" t="n">
-        <v>6427793</v>
+        <v>6427693</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3447,10 +3447,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124911742</v>
+        <v>124911723</v>
       </c>
       <c r="B25" t="n">
-        <v>74885</v>
+        <v>74893</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3459,25 +3459,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6439</v>
+        <v>308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3538,6 +3538,21 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
@@ -3553,10 +3568,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124911723</v>
+        <v>124911842</v>
       </c>
       <c r="B26" t="n">
-        <v>74893</v>
+        <v>79851</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3565,25 +3580,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>308</v>
+        <v>229497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3592,14 +3607,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos20, Vg</t>
+          <t>Middagsmärker 1:1 pos22, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>432181</v>
+        <v>431972</v>
       </c>
       <c r="R26" t="n">
-        <v>6427847</v>
+        <v>6427781</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3646,17 +3661,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3674,10 +3689,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124911784</v>
+        <v>124911742</v>
       </c>
       <c r="B27" t="n">
-        <v>95335</v>
+        <v>74885</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3690,38 +3705,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2809</v>
+        <v>6439</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 21, Vg</t>
+          <t>Middagsmärket 1:1 pos20, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>432143</v>
+        <v>432181</v>
       </c>
       <c r="R27" t="n">
-        <v>6427793</v>
+        <v>6427847</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3754,11 +3768,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3786,10 +3795,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124911842</v>
+        <v>124911784</v>
       </c>
       <c r="B28" t="n">
-        <v>79851</v>
+        <v>95335</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3802,37 +3811,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229497</v>
+        <v>2809</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos22, Vg</t>
+          <t>Middagsmärket 1:1 pos 21, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>431972</v>
+        <v>432143</v>
       </c>
       <c r="R28" t="n">
-        <v>6427781</v>
+        <v>6427793</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3867,6 +3877,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3876,21 +3891,6 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3907,10 +3907,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124911863</v>
+        <v>124911802</v>
       </c>
       <c r="B29" t="n">
-        <v>79936</v>
+        <v>79851</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3919,25 +3919,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229504</v>
+        <v>229497</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3946,14 +3946,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 123, Vg</t>
+          <t>Middagsmärker 1:1 pos 19, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>431964</v>
+        <v>432154</v>
       </c>
       <c r="R29" t="n">
-        <v>6427784</v>
+        <v>6427796</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4000,17 +4000,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -2354,10 +2354,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124883023</v>
+        <v>124883045</v>
       </c>
       <c r="B16" t="n">
-        <v>79851</v>
+        <v>79319</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2366,25 +2366,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>1026</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2393,14 +2393,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos18, Vg</t>
+          <t>Middagsmärker 1:1 pos 19, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432235</v>
+        <v>432154</v>
       </c>
       <c r="R16" t="n">
-        <v>6427836</v>
+        <v>6427796</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2435,11 +2435,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På en hasselstam direkt intill den stora aspen med lunglav, ädellav och korallblylav (samma koordinat - se bilder för lunglaven).</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2452,17 +2447,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>hassel</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Corylus avellana</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Corylus avellana</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2480,10 +2475,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124779232</v>
+        <v>124882917</v>
       </c>
       <c r="B17" t="n">
-        <v>95551</v>
+        <v>79851</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2496,46 +2491,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>210</v>
+        <v>229497</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Smedstorp 1:1 pos54, Vg</t>
+          <t>Middagsmärket 1:1 pos18, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431805</v>
+        <v>432235</v>
       </c>
       <c r="R17" t="n">
-        <v>6427767</v>
+        <v>6427836</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2570,6 +2556,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2579,6 +2570,21 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2595,10 +2601,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124883045</v>
+        <v>124779232</v>
       </c>
       <c r="B18" t="n">
-        <v>79319</v>
+        <v>95551</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2607,41 +2613,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1026</v>
+        <v>210</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos 19, Vg</t>
+          <t>Smedstorp 1:1 pos54, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>432154</v>
+        <v>431805</v>
       </c>
       <c r="R18" t="n">
-        <v>6427796</v>
+        <v>6427767</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2685,21 +2700,6 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2716,10 +2716,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124882863</v>
+        <v>124882964</v>
       </c>
       <c r="B19" t="n">
-        <v>79319</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2728,25 +2728,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1026</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2797,11 +2797,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2842,10 +2837,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124882964</v>
+        <v>124882863</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>79319</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2854,25 +2849,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1026</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2923,6 +2918,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2963,10 +2963,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124911853</v>
+        <v>124911788</v>
       </c>
       <c r="B21" t="n">
-        <v>79936</v>
+        <v>79851</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2975,25 +2975,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229504</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3002,14 +3002,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos22, Vg</t>
+          <t>Middagsmärket 1:1 pos 21, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>431972</v>
+        <v>432143</v>
       </c>
       <c r="R21" t="n">
-        <v>6427781</v>
+        <v>6427793</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3056,17 +3056,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3084,7 +3084,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124911788</v>
+        <v>124911842</v>
       </c>
       <c r="B22" t="n">
         <v>79851</v>
@@ -3123,14 +3123,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 21, Vg</t>
+          <t>Middagsmärker 1:1 pos22, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>432143</v>
+        <v>431972</v>
       </c>
       <c r="R22" t="n">
-        <v>6427793</v>
+        <v>6427781</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3177,17 +3177,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3205,10 +3205,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124911863</v>
+        <v>124911784</v>
       </c>
       <c r="B23" t="n">
-        <v>79936</v>
+        <v>95335</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3217,41 +3217,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229504</v>
+        <v>2809</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 123, Vg</t>
+          <t>Middagsmärket 1:1 pos 21, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431964</v>
+        <v>432143</v>
       </c>
       <c r="R23" t="n">
-        <v>6427784</v>
+        <v>6427793</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3286,6 +3287,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3295,21 +3301,6 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3326,10 +3317,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124911865</v>
+        <v>124911853</v>
       </c>
       <c r="B24" t="n">
-        <v>79190</v>
+        <v>79936</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3338,25 +3329,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6431</v>
+        <v>229504</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3365,14 +3356,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos25, Vg</t>
+          <t>Middagsmärker 1:1 pos22, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>431886</v>
+        <v>431972</v>
       </c>
       <c r="R24" t="n">
-        <v>6427693</v>
+        <v>6427781</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3419,17 +3410,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3447,10 +3438,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124911723</v>
+        <v>124911742</v>
       </c>
       <c r="B25" t="n">
-        <v>74893</v>
+        <v>74885</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3459,25 +3450,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3538,21 +3529,6 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
@@ -3568,7 +3544,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124911842</v>
+        <v>124911802</v>
       </c>
       <c r="B26" t="n">
         <v>79851</v>
@@ -3607,14 +3583,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos22, Vg</t>
+          <t>Middagsmärker 1:1 pos 19, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>431972</v>
+        <v>432154</v>
       </c>
       <c r="R26" t="n">
-        <v>6427781</v>
+        <v>6427796</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3661,17 +3637,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3689,10 +3665,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124911742</v>
+        <v>124911865</v>
       </c>
       <c r="B27" t="n">
-        <v>74885</v>
+        <v>79190</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3705,21 +3681,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6439</v>
+        <v>6431</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3728,14 +3704,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos20, Vg</t>
+          <t>Middagsmärket 1:1 pos25, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>432181</v>
+        <v>431886</v>
       </c>
       <c r="R27" t="n">
-        <v>6427847</v>
+        <v>6427693</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3779,6 +3755,21 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3795,10 +3786,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124911784</v>
+        <v>124911723</v>
       </c>
       <c r="B28" t="n">
-        <v>95335</v>
+        <v>74893</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3807,42 +3798,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2809</v>
+        <v>308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 21, Vg</t>
+          <t>Middagsmärket 1:1 pos20, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>432143</v>
+        <v>432181</v>
       </c>
       <c r="R28" t="n">
-        <v>6427793</v>
+        <v>6427847</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3877,11 +3867,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3891,6 +3876,21 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3907,10 +3907,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124911802</v>
+        <v>124911863</v>
       </c>
       <c r="B29" t="n">
-        <v>79851</v>
+        <v>79936</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3919,25 +3919,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>229504</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3946,14 +3946,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos 19, Vg</t>
+          <t>Middagsmärket 1:1 pos 123, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>432154</v>
+        <v>431964</v>
       </c>
       <c r="R29" t="n">
-        <v>6427796</v>
+        <v>6427784</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4000,17 +4000,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -2601,10 +2601,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124779232</v>
+        <v>124882863</v>
       </c>
       <c r="B18" t="n">
-        <v>95551</v>
+        <v>79319</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2613,50 +2613,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>210</v>
+        <v>1026</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Smedstorp 1:1 pos54, Vg</t>
+          <t>Middagsmärket 1:1 pos18, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431805</v>
+        <v>432235</v>
       </c>
       <c r="R18" t="n">
-        <v>6427767</v>
+        <v>6427836</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2691,6 +2682,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2700,6 +2696,21 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2716,10 +2727,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124882964</v>
+        <v>124779232</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>95551</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2728,41 +2739,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>210</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos18, Vg</t>
+          <t>Smedstorp 1:1 pos54, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432235</v>
+        <v>431805</v>
       </c>
       <c r="R19" t="n">
-        <v>6427836</v>
+        <v>6427767</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2806,21 +2826,6 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2837,10 +2842,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124882863</v>
+        <v>124882964</v>
       </c>
       <c r="B20" t="n">
-        <v>79319</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2849,25 +2854,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1026</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2918,11 +2923,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2963,10 +2963,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124911788</v>
+        <v>124911784</v>
       </c>
       <c r="B21" t="n">
-        <v>79851</v>
+        <v>95335</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2979,26 +2979,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>2809</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3044,6 +3045,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3053,21 +3059,6 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3205,10 +3196,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124911784</v>
+        <v>124911802</v>
       </c>
       <c r="B23" t="n">
-        <v>95335</v>
+        <v>79851</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3221,38 +3212,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2809</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 21, Vg</t>
+          <t>Middagsmärker 1:1 pos 19, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>432143</v>
+        <v>432154</v>
       </c>
       <c r="R23" t="n">
-        <v>6427793</v>
+        <v>6427796</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3287,11 +3277,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3301,6 +3286,21 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3317,7 +3317,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124911853</v>
+        <v>124911863</v>
       </c>
       <c r="B24" t="n">
         <v>79936</v>
@@ -3356,14 +3356,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos22, Vg</t>
+          <t>Middagsmärket 1:1 pos 123, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>431972</v>
+        <v>431964</v>
       </c>
       <c r="R24" t="n">
-        <v>6427781</v>
+        <v>6427784</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124911742</v>
+        <v>124911853</v>
       </c>
       <c r="B25" t="n">
-        <v>74885</v>
+        <v>79936</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3450,25 +3450,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6439</v>
+        <v>229504</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3477,14 +3477,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos20, Vg</t>
+          <t>Middagsmärker 1:1 pos22, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>432181</v>
+        <v>431972</v>
       </c>
       <c r="R25" t="n">
-        <v>6427847</v>
+        <v>6427781</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3528,6 +3528,21 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3544,7 +3559,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124911802</v>
+        <v>124911788</v>
       </c>
       <c r="B26" t="n">
         <v>79851</v>
@@ -3583,14 +3598,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos 19, Vg</t>
+          <t>Middagsmärket 1:1 pos 21, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>432154</v>
+        <v>432143</v>
       </c>
       <c r="R26" t="n">
-        <v>6427796</v>
+        <v>6427793</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3786,10 +3801,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124911723</v>
+        <v>124911742</v>
       </c>
       <c r="B28" t="n">
-        <v>74893</v>
+        <v>74885</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3798,25 +3813,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3877,21 +3892,6 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
@@ -3907,10 +3907,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124911863</v>
+        <v>124911723</v>
       </c>
       <c r="B29" t="n">
-        <v>79936</v>
+        <v>74893</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3923,21 +3923,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229504</v>
+        <v>308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3946,14 +3946,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 123, Vg</t>
+          <t>Middagsmärket 1:1 pos20, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>431964</v>
+        <v>432181</v>
       </c>
       <c r="R29" t="n">
-        <v>6427784</v>
+        <v>6427847</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4000,17 +4000,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -2354,7 +2354,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124883045</v>
+        <v>124882863</v>
       </c>
       <c r="B16" t="n">
         <v>79319</v>
@@ -2393,14 +2393,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos 19, Vg</t>
+          <t>Middagsmärket 1:1 pos18, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432154</v>
+        <v>432235</v>
       </c>
       <c r="R16" t="n">
-        <v>6427796</v>
+        <v>6427836</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2433,6 +2433,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2601,10 +2606,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124882863</v>
+        <v>124779232</v>
       </c>
       <c r="B18" t="n">
-        <v>79319</v>
+        <v>95551</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2613,41 +2618,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1026</v>
+        <v>210</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos18, Vg</t>
+          <t>Smedstorp 1:1 pos54, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>432235</v>
+        <v>431805</v>
       </c>
       <c r="R18" t="n">
-        <v>6427836</v>
+        <v>6427767</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2682,11 +2696,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2696,21 +2705,6 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2727,10 +2721,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124779232</v>
+        <v>124883045</v>
       </c>
       <c r="B19" t="n">
-        <v>95551</v>
+        <v>79319</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2739,50 +2733,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>210</v>
+        <v>1026</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Smedstorp 1:1 pos54, Vg</t>
+          <t>Middagsmärker 1:1 pos 19, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>431805</v>
+        <v>432154</v>
       </c>
       <c r="R19" t="n">
-        <v>6427767</v>
+        <v>6427796</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2826,6 +2811,21 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2963,10 +2963,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124911784</v>
+        <v>124911788</v>
       </c>
       <c r="B21" t="n">
-        <v>95335</v>
+        <v>79851</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2979,27 +2979,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2809</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3045,11 +3044,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3059,6 +3053,21 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3075,10 +3084,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124911842</v>
+        <v>124911784</v>
       </c>
       <c r="B22" t="n">
-        <v>79851</v>
+        <v>95335</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3091,37 +3100,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>2809</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos22, Vg</t>
+          <t>Middagsmärket 1:1 pos 21, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431972</v>
+        <v>432143</v>
       </c>
       <c r="R22" t="n">
-        <v>6427781</v>
+        <v>6427793</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3156,6 +3166,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3165,21 +3180,6 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3196,10 +3196,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124911802</v>
+        <v>124911863</v>
       </c>
       <c r="B23" t="n">
-        <v>79851</v>
+        <v>79936</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3208,25 +3208,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>229504</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3235,14 +3235,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos 19, Vg</t>
+          <t>Middagsmärket 1:1 pos 123, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>432154</v>
+        <v>431964</v>
       </c>
       <c r="R23" t="n">
-        <v>6427796</v>
+        <v>6427784</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3289,17 +3289,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124911863</v>
+        <v>124911723</v>
       </c>
       <c r="B24" t="n">
-        <v>79936</v>
+        <v>74893</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3333,21 +3333,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229504</v>
+        <v>308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3356,14 +3356,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 123, Vg</t>
+          <t>Middagsmärket 1:1 pos20, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>431964</v>
+        <v>432181</v>
       </c>
       <c r="R24" t="n">
-        <v>6427784</v>
+        <v>6427847</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3410,17 +3410,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124911853</v>
+        <v>124911842</v>
       </c>
       <c r="B25" t="n">
-        <v>79936</v>
+        <v>79851</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3450,25 +3450,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229504</v>
+        <v>229497</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3559,10 +3559,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124911788</v>
+        <v>124911742</v>
       </c>
       <c r="B26" t="n">
-        <v>79851</v>
+        <v>74885</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3575,21 +3575,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>6439</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3598,14 +3598,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 21, Vg</t>
+          <t>Middagsmärket 1:1 pos20, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>432143</v>
+        <v>432181</v>
       </c>
       <c r="R26" t="n">
-        <v>6427793</v>
+        <v>6427847</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3649,21 +3649,6 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3680,10 +3665,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124911865</v>
+        <v>124911802</v>
       </c>
       <c r="B27" t="n">
-        <v>79190</v>
+        <v>79851</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3696,21 +3681,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6431</v>
+        <v>229497</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3719,14 +3704,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos25, Vg</t>
+          <t>Middagsmärker 1:1 pos 19, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>431886</v>
+        <v>432154</v>
       </c>
       <c r="R27" t="n">
-        <v>6427693</v>
+        <v>6427796</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3801,10 +3786,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124911742</v>
+        <v>124911853</v>
       </c>
       <c r="B28" t="n">
-        <v>74885</v>
+        <v>79936</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3813,25 +3798,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6439</v>
+        <v>229504</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3840,14 +3825,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos20, Vg</t>
+          <t>Middagsmärker 1:1 pos22, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>432181</v>
+        <v>431972</v>
       </c>
       <c r="R28" t="n">
-        <v>6427847</v>
+        <v>6427781</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3891,6 +3876,21 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3907,10 +3907,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124911723</v>
+        <v>124911865</v>
       </c>
       <c r="B29" t="n">
-        <v>74893</v>
+        <v>79190</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3919,25 +3919,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>308</v>
+        <v>6431</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3946,14 +3946,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos20, Vg</t>
+          <t>Middagsmärket 1:1 pos25, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>432181</v>
+        <v>431886</v>
       </c>
       <c r="R29" t="n">
-        <v>6427847</v>
+        <v>6427693</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4000,17 +4000,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -3317,10 +3317,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124911723</v>
+        <v>124911842</v>
       </c>
       <c r="B24" t="n">
-        <v>74893</v>
+        <v>79851</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3329,25 +3329,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>308</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3356,14 +3356,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos20, Vg</t>
+          <t>Middagsmärker 1:1 pos22, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>432181</v>
+        <v>431972</v>
       </c>
       <c r="R24" t="n">
-        <v>6427847</v>
+        <v>6427781</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3410,17 +3410,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124911842</v>
+        <v>124911723</v>
       </c>
       <c r="B25" t="n">
-        <v>79851</v>
+        <v>74893</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3450,25 +3450,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3477,14 +3477,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos22, Vg</t>
+          <t>Middagsmärket 1:1 pos20, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>431972</v>
+        <v>432181</v>
       </c>
       <c r="R25" t="n">
-        <v>6427781</v>
+        <v>6427847</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3531,17 +3531,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -2354,10 +2354,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124882863</v>
+        <v>124883023</v>
       </c>
       <c r="B16" t="n">
-        <v>79319</v>
+        <v>79851</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2366,25 +2366,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1026</v>
+        <v>229497</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
+          <t>På en hasselstam direkt intill den stora aspen med lunglav, ädellav och korallblylav (samma koordinat - se bilder för lunglaven).</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2452,17 +2452,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>hassel</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Corylus avellana</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Corylus avellana</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124882917</v>
+        <v>124779232</v>
       </c>
       <c r="B17" t="n">
-        <v>79851</v>
+        <v>95551</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2496,37 +2496,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos18, Vg</t>
+          <t>Smedstorp 1:1 pos54, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432235</v>
+        <v>431805</v>
       </c>
       <c r="R17" t="n">
-        <v>6427836</v>
+        <v>6427767</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2561,11 +2570,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2575,21 +2579,6 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2606,10 +2595,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124779232</v>
+        <v>124883045</v>
       </c>
       <c r="B18" t="n">
-        <v>95551</v>
+        <v>79319</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2618,50 +2607,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>210</v>
+        <v>1026</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Smedstorp 1:1 pos54, Vg</t>
+          <t>Middagsmärker 1:1 pos 19, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431805</v>
+        <v>432154</v>
       </c>
       <c r="R18" t="n">
-        <v>6427767</v>
+        <v>6427796</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2705,6 +2685,21 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2721,10 +2716,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124883045</v>
+        <v>124882964</v>
       </c>
       <c r="B19" t="n">
-        <v>79319</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2733,25 +2728,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1026</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2760,14 +2755,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos 19, Vg</t>
+          <t>Middagsmärket 1:1 pos18, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432154</v>
+        <v>432235</v>
       </c>
       <c r="R19" t="n">
-        <v>6427796</v>
+        <v>6427836</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2842,10 +2837,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124882964</v>
+        <v>124882863</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>79319</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2854,25 +2849,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1026</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2923,6 +2918,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3084,10 +3084,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124911784</v>
+        <v>124911853</v>
       </c>
       <c r="B22" t="n">
-        <v>95335</v>
+        <v>79936</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3096,42 +3096,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2809</v>
+        <v>229504</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 21, Vg</t>
+          <t>Middagsmärker 1:1 pos22, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>432143</v>
+        <v>431972</v>
       </c>
       <c r="R22" t="n">
-        <v>6427793</v>
+        <v>6427781</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3166,11 +3165,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3180,6 +3174,21 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3196,10 +3205,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124911863</v>
+        <v>124911842</v>
       </c>
       <c r="B23" t="n">
-        <v>79936</v>
+        <v>79851</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3208,25 +3217,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229504</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3235,14 +3244,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 123, Vg</t>
+          <t>Middagsmärker 1:1 pos22, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431964</v>
+        <v>431972</v>
       </c>
       <c r="R23" t="n">
-        <v>6427784</v>
+        <v>6427781</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3317,7 +3326,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124911842</v>
+        <v>124911802</v>
       </c>
       <c r="B24" t="n">
         <v>79851</v>
@@ -3356,14 +3365,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos22, Vg</t>
+          <t>Middagsmärker 1:1 pos 19, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>431972</v>
+        <v>432154</v>
       </c>
       <c r="R24" t="n">
-        <v>6427781</v>
+        <v>6427796</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3410,17 +3419,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3438,10 +3447,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124911723</v>
+        <v>124911865</v>
       </c>
       <c r="B25" t="n">
-        <v>74893</v>
+        <v>79190</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3450,25 +3459,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>308</v>
+        <v>6431</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3477,14 +3486,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos20, Vg</t>
+          <t>Middagsmärket 1:1 pos25, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>432181</v>
+        <v>431886</v>
       </c>
       <c r="R25" t="n">
-        <v>6427847</v>
+        <v>6427693</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3531,17 +3540,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3665,10 +3674,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124911802</v>
+        <v>124911723</v>
       </c>
       <c r="B27" t="n">
-        <v>79851</v>
+        <v>74893</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3677,25 +3686,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229497</v>
+        <v>308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3704,14 +3713,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos 19, Vg</t>
+          <t>Middagsmärket 1:1 pos20, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>432154</v>
+        <v>432181</v>
       </c>
       <c r="R27" t="n">
-        <v>6427796</v>
+        <v>6427847</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3758,17 +3767,17 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3786,7 +3795,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124911853</v>
+        <v>124911863</v>
       </c>
       <c r="B28" t="n">
         <v>79936</v>
@@ -3825,14 +3834,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos22, Vg</t>
+          <t>Middagsmärket 1:1 pos 123, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>431972</v>
+        <v>431964</v>
       </c>
       <c r="R28" t="n">
-        <v>6427781</v>
+        <v>6427784</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3907,10 +3916,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124911865</v>
+        <v>124911784</v>
       </c>
       <c r="B29" t="n">
-        <v>79190</v>
+        <v>95335</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3923,37 +3932,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6431</v>
+        <v>2809</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos25, Vg</t>
+          <t>Middagsmärket 1:1 pos 21, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>431886</v>
+        <v>432143</v>
       </c>
       <c r="R29" t="n">
-        <v>6427693</v>
+        <v>6427793</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3988,6 +3998,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3997,21 +4012,6 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -2354,10 +2354,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124883023</v>
+        <v>124779232</v>
       </c>
       <c r="B16" t="n">
-        <v>79851</v>
+        <v>95551</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2370,37 +2370,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos18, Vg</t>
+          <t>Smedstorp 1:1 pos54, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432235</v>
+        <v>431805</v>
       </c>
       <c r="R16" t="n">
-        <v>6427836</v>
+        <v>6427767</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2435,11 +2444,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På en hasselstam direkt intill den stora aspen med lunglav, ädellav och korallblylav (samma koordinat - se bilder för lunglaven).</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2449,21 +2453,6 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>hassel</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2480,10 +2469,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124779232</v>
+        <v>124882863</v>
       </c>
       <c r="B17" t="n">
-        <v>95551</v>
+        <v>79319</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2492,50 +2481,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>210</v>
+        <v>1026</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Smedstorp 1:1 pos54, Vg</t>
+          <t>Middagsmärket 1:1 pos18, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431805</v>
+        <v>432235</v>
       </c>
       <c r="R17" t="n">
-        <v>6427767</v>
+        <v>6427836</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2570,6 +2550,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2579,6 +2564,21 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2716,10 +2716,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124882964</v>
+        <v>124882917</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>79851</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2728,25 +2728,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2797,6 +2797,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2837,10 +2842,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124882863</v>
+        <v>124882964</v>
       </c>
       <c r="B20" t="n">
-        <v>79319</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2849,25 +2854,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1026</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2918,11 +2923,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124911788</v>
+        <v>124911802</v>
       </c>
       <c r="B21" t="n">
         <v>79851</v>
@@ -3002,14 +3002,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 21, Vg</t>
+          <t>Middagsmärker 1:1 pos 19, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>432143</v>
+        <v>432154</v>
       </c>
       <c r="R21" t="n">
-        <v>6427793</v>
+        <v>6427796</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3084,10 +3084,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124911853</v>
+        <v>124911842</v>
       </c>
       <c r="B22" t="n">
-        <v>79936</v>
+        <v>79851</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3096,25 +3096,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229504</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3205,10 +3205,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124911842</v>
+        <v>124911865</v>
       </c>
       <c r="B23" t="n">
-        <v>79851</v>
+        <v>79190</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3221,21 +3221,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>6431</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3244,14 +3244,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos22, Vg</t>
+          <t>Middagsmärket 1:1 pos25, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431972</v>
+        <v>431886</v>
       </c>
       <c r="R23" t="n">
-        <v>6427781</v>
+        <v>6427693</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3298,17 +3298,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3326,10 +3326,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124911802</v>
+        <v>124911863</v>
       </c>
       <c r="B24" t="n">
-        <v>79851</v>
+        <v>79936</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3338,25 +3338,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>229504</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3365,14 +3365,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos 19, Vg</t>
+          <t>Middagsmärket 1:1 pos 123, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>432154</v>
+        <v>431964</v>
       </c>
       <c r="R24" t="n">
-        <v>6427796</v>
+        <v>6427784</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3419,17 +3419,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124911865</v>
+        <v>124911742</v>
       </c>
       <c r="B25" t="n">
-        <v>79190</v>
+        <v>74885</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3463,21 +3463,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6431</v>
+        <v>6439</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3486,14 +3486,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos25, Vg</t>
+          <t>Middagsmärket 1:1 pos20, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>431886</v>
+        <v>432181</v>
       </c>
       <c r="R25" t="n">
-        <v>6427693</v>
+        <v>6427847</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3537,21 +3537,6 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3568,10 +3553,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124911742</v>
+        <v>124911853</v>
       </c>
       <c r="B26" t="n">
-        <v>74885</v>
+        <v>79936</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3580,25 +3565,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6439</v>
+        <v>229504</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3607,14 +3592,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos20, Vg</t>
+          <t>Middagsmärker 1:1 pos22, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>432181</v>
+        <v>431972</v>
       </c>
       <c r="R26" t="n">
-        <v>6427847</v>
+        <v>6427781</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3658,6 +3643,21 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3795,10 +3795,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124911863</v>
+        <v>124911788</v>
       </c>
       <c r="B28" t="n">
-        <v>79936</v>
+        <v>79851</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3807,25 +3807,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229504</v>
+        <v>229497</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3834,14 +3834,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 123, Vg</t>
+          <t>Middagsmärket 1:1 pos 21, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>431964</v>
+        <v>432143</v>
       </c>
       <c r="R28" t="n">
-        <v>6427784</v>
+        <v>6427793</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3888,17 +3888,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -2354,10 +2354,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124779232</v>
+        <v>124883023</v>
       </c>
       <c r="B16" t="n">
-        <v>95551</v>
+        <v>79988</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2370,46 +2370,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>210</v>
+        <v>229497</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Smedstorp 1:1 pos54, Vg</t>
+          <t>Middagsmärket 1:1 pos18, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431805</v>
+        <v>432235</v>
       </c>
       <c r="R16" t="n">
-        <v>6427767</v>
+        <v>6427836</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2444,6 +2435,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På en hasselstam direkt intill den stora aspen med lunglav, ädellav och korallblylav (samma koordinat - se bilder för lunglaven).</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2453,6 +2449,21 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2472,7 +2483,7 @@
         <v>124882863</v>
       </c>
       <c r="B17" t="n">
-        <v>79319</v>
+        <v>79456</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2595,10 +2606,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124883045</v>
+        <v>124882964</v>
       </c>
       <c r="B18" t="n">
-        <v>79319</v>
+        <v>80028</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2607,25 +2618,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1026</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2634,14 +2645,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos 19, Vg</t>
+          <t>Middagsmärket 1:1 pos18, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>432154</v>
+        <v>432235</v>
       </c>
       <c r="R18" t="n">
-        <v>6427796</v>
+        <v>6427836</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2716,10 +2727,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124882917</v>
+        <v>124883045</v>
       </c>
       <c r="B19" t="n">
-        <v>79851</v>
+        <v>79456</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2728,25 +2739,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>1026</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2755,14 +2766,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos18, Vg</t>
+          <t>Middagsmärker 1:1 pos 19, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432235</v>
+        <v>432154</v>
       </c>
       <c r="R19" t="n">
-        <v>6427836</v>
+        <v>6427796</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2795,11 +2806,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2842,10 +2848,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124882964</v>
+        <v>124779232</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>95719</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2854,41 +2860,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>210</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos18, Vg</t>
+          <t>Smedstorp 1:1 pos54, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>432235</v>
+        <v>431805</v>
       </c>
       <c r="R20" t="n">
-        <v>6427836</v>
+        <v>6427767</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2932,21 +2947,6 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2963,10 +2963,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124911802</v>
+        <v>124911863</v>
       </c>
       <c r="B21" t="n">
-        <v>79851</v>
+        <v>80073</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2975,25 +2975,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>229504</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3002,14 +3002,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos 19, Vg</t>
+          <t>Middagsmärket 1:1 pos 123, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>432154</v>
+        <v>431964</v>
       </c>
       <c r="R21" t="n">
-        <v>6427796</v>
+        <v>6427784</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3056,17 +3056,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3084,10 +3084,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124911842</v>
+        <v>124911723</v>
       </c>
       <c r="B22" t="n">
-        <v>79851</v>
+        <v>75017</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3096,25 +3096,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3123,14 +3123,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos22, Vg</t>
+          <t>Middagsmärket 1:1 pos20, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431972</v>
+        <v>432181</v>
       </c>
       <c r="R22" t="n">
-        <v>6427781</v>
+        <v>6427847</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3177,17 +3177,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3205,10 +3205,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124911865</v>
+        <v>124911802</v>
       </c>
       <c r="B23" t="n">
-        <v>79190</v>
+        <v>79988</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3221,21 +3221,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6431</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3244,14 +3244,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos25, Vg</t>
+          <t>Middagsmärker 1:1 pos 19, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431886</v>
+        <v>432154</v>
       </c>
       <c r="R23" t="n">
-        <v>6427693</v>
+        <v>6427796</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3326,10 +3326,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124911863</v>
+        <v>124911742</v>
       </c>
       <c r="B24" t="n">
-        <v>79936</v>
+        <v>75009</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3338,25 +3338,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229504</v>
+        <v>6439</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3365,14 +3365,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 123, Vg</t>
+          <t>Middagsmärket 1:1 pos20, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>431964</v>
+        <v>432181</v>
       </c>
       <c r="R24" t="n">
-        <v>6427784</v>
+        <v>6427847</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3416,21 +3416,6 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3447,10 +3432,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124911742</v>
+        <v>124911853</v>
       </c>
       <c r="B25" t="n">
-        <v>74885</v>
+        <v>80073</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3459,25 +3444,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6439</v>
+        <v>229504</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3486,14 +3471,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos20, Vg</t>
+          <t>Middagsmärker 1:1 pos22, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>432181</v>
+        <v>431972</v>
       </c>
       <c r="R25" t="n">
-        <v>6427847</v>
+        <v>6427781</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3537,6 +3522,21 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3553,10 +3553,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124911853</v>
+        <v>124911784</v>
       </c>
       <c r="B26" t="n">
-        <v>79936</v>
+        <v>95503</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3565,41 +3565,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229504</v>
+        <v>2809</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos22, Vg</t>
+          <t>Middagsmärket 1:1 pos 21, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>431972</v>
+        <v>432143</v>
       </c>
       <c r="R26" t="n">
-        <v>6427781</v>
+        <v>6427793</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3634,6 +3635,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3643,21 +3649,6 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3674,10 +3665,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124911723</v>
+        <v>124911865</v>
       </c>
       <c r="B27" t="n">
-        <v>74893</v>
+        <v>79327</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3686,25 +3677,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>308</v>
+        <v>6431</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3713,14 +3704,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos20, Vg</t>
+          <t>Middagsmärket 1:1 pos25, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>432181</v>
+        <v>431886</v>
       </c>
       <c r="R27" t="n">
-        <v>6427847</v>
+        <v>6427693</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3767,17 +3758,17 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3798,7 +3789,7 @@
         <v>124911788</v>
       </c>
       <c r="B28" t="n">
-        <v>79851</v>
+        <v>79988</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3916,10 +3907,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124911784</v>
+        <v>124911842</v>
       </c>
       <c r="B29" t="n">
-        <v>95335</v>
+        <v>79988</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3932,38 +3923,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2809</v>
+        <v>229497</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 21, Vg</t>
+          <t>Middagsmärker 1:1 pos22, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>432143</v>
+        <v>431972</v>
       </c>
       <c r="R29" t="n">
-        <v>6427793</v>
+        <v>6427781</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3998,11 +3988,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4012,6 +3997,21 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -2354,10 +2354,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124883023</v>
+        <v>124779232</v>
       </c>
       <c r="B16" t="n">
-        <v>79988</v>
+        <v>95719</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2370,37 +2370,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos18, Vg</t>
+          <t>Smedstorp 1:1 pos54, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432235</v>
+        <v>431805</v>
       </c>
       <c r="R16" t="n">
-        <v>6427836</v>
+        <v>6427767</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2435,11 +2444,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På en hasselstam direkt intill den stora aspen med lunglav, ädellav och korallblylav (samma koordinat - se bilder för lunglaven).</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2449,21 +2453,6 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>hassel</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2480,10 +2469,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124882863</v>
+        <v>124882917</v>
       </c>
       <c r="B17" t="n">
-        <v>79456</v>
+        <v>79988</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2492,25 +2481,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1026</v>
+        <v>229497</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2606,10 +2595,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124882964</v>
+        <v>124883045</v>
       </c>
       <c r="B18" t="n">
-        <v>80028</v>
+        <v>79456</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2618,25 +2607,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1026</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2645,14 +2634,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos18, Vg</t>
+          <t>Middagsmärker 1:1 pos 19, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>432235</v>
+        <v>432154</v>
       </c>
       <c r="R18" t="n">
-        <v>6427836</v>
+        <v>6427796</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2727,7 +2716,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124883045</v>
+        <v>124882863</v>
       </c>
       <c r="B19" t="n">
         <v>79456</v>
@@ -2766,14 +2755,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos 19, Vg</t>
+          <t>Middagsmärket 1:1 pos18, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432154</v>
+        <v>432235</v>
       </c>
       <c r="R19" t="n">
-        <v>6427796</v>
+        <v>6427836</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2806,6 +2795,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2848,10 +2842,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124779232</v>
+        <v>124882964</v>
       </c>
       <c r="B20" t="n">
-        <v>95719</v>
+        <v>80028</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2860,50 +2854,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>210</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Smedstorp 1:1 pos54, Vg</t>
+          <t>Middagsmärket 1:1 pos18, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>431805</v>
+        <v>432235</v>
       </c>
       <c r="R20" t="n">
-        <v>6427767</v>
+        <v>6427836</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2947,6 +2932,21 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2963,10 +2963,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124911863</v>
+        <v>124911788</v>
       </c>
       <c r="B21" t="n">
-        <v>80073</v>
+        <v>79988</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2975,25 +2975,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229504</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3002,14 +3002,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 123, Vg</t>
+          <t>Middagsmärket 1:1 pos 21, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>431964</v>
+        <v>432143</v>
       </c>
       <c r="R21" t="n">
-        <v>6427784</v>
+        <v>6427793</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3056,17 +3056,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3084,10 +3084,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124911723</v>
+        <v>124911742</v>
       </c>
       <c r="B22" t="n">
-        <v>75017</v>
+        <v>75009</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3096,25 +3096,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3175,21 +3175,6 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
@@ -3205,10 +3190,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124911802</v>
+        <v>124911723</v>
       </c>
       <c r="B23" t="n">
-        <v>79988</v>
+        <v>75017</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3217,25 +3202,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3244,14 +3229,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos 19, Vg</t>
+          <t>Middagsmärket 1:1 pos20, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>432154</v>
+        <v>432181</v>
       </c>
       <c r="R23" t="n">
-        <v>6427796</v>
+        <v>6427847</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3298,17 +3283,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3326,10 +3311,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124911742</v>
+        <v>124911863</v>
       </c>
       <c r="B24" t="n">
-        <v>75009</v>
+        <v>80073</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3338,25 +3323,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6439</v>
+        <v>229504</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3365,14 +3350,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos20, Vg</t>
+          <t>Middagsmärket 1:1 pos 123, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>432181</v>
+        <v>431964</v>
       </c>
       <c r="R24" t="n">
-        <v>6427847</v>
+        <v>6427784</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3416,6 +3401,21 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3553,10 +3553,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124911784</v>
+        <v>124911865</v>
       </c>
       <c r="B26" t="n">
-        <v>95503</v>
+        <v>79327</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3569,38 +3569,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2809</v>
+        <v>6431</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 21, Vg</t>
+          <t>Middagsmärket 1:1 pos25, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>432143</v>
+        <v>431886</v>
       </c>
       <c r="R26" t="n">
-        <v>6427793</v>
+        <v>6427693</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3635,11 +3634,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3649,6 +3643,21 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3665,10 +3674,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124911865</v>
+        <v>124911784</v>
       </c>
       <c r="B27" t="n">
-        <v>79327</v>
+        <v>95503</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3681,37 +3690,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6431</v>
+        <v>2809</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos25, Vg</t>
+          <t>Middagsmärket 1:1 pos 21, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>431886</v>
+        <v>432143</v>
       </c>
       <c r="R27" t="n">
-        <v>6427693</v>
+        <v>6427793</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3746,6 +3756,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3755,21 +3770,6 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3786,7 +3786,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124911788</v>
+        <v>124911802</v>
       </c>
       <c r="B28" t="n">
         <v>79988</v>
@@ -3825,14 +3825,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 21, Vg</t>
+          <t>Middagsmärker 1:1 pos 19, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>432143</v>
+        <v>432154</v>
       </c>
       <c r="R28" t="n">
-        <v>6427793</v>
+        <v>6427796</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -2963,10 +2963,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124911788</v>
+        <v>124911742</v>
       </c>
       <c r="B21" t="n">
-        <v>79988</v>
+        <v>75009</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2979,21 +2979,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>6439</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3002,14 +3002,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 21, Vg</t>
+          <t>Middagsmärket 1:1 pos20, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>432143</v>
+        <v>432181</v>
       </c>
       <c r="R21" t="n">
-        <v>6427793</v>
+        <v>6427847</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3053,21 +3053,6 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3084,10 +3069,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124911742</v>
+        <v>124911723</v>
       </c>
       <c r="B22" t="n">
-        <v>75009</v>
+        <v>75017</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3096,25 +3081,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6439</v>
+        <v>308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3175,6 +3160,21 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
@@ -3190,10 +3190,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124911723</v>
+        <v>124911788</v>
       </c>
       <c r="B23" t="n">
-        <v>75017</v>
+        <v>79988</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3202,25 +3202,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>308</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3229,14 +3229,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos20, Vg</t>
+          <t>Middagsmärket 1:1 pos 21, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>432181</v>
+        <v>432143</v>
       </c>
       <c r="R23" t="n">
-        <v>6427847</v>
+        <v>6427793</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3283,17 +3283,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -2354,62 +2354,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124779232</v>
+        <v>124882964</v>
       </c>
       <c r="B16" t="n">
-        <v>95719</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>210</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Smedstorp 1:1 pos54, Vg</t>
+          <t>Middagsmärket 1:1 pos18, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431805</v>
+        <v>432235</v>
       </c>
       <c r="R16" t="n">
-        <v>6427767</v>
+        <v>6427836</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2453,6 +2439,21 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2469,15 +2470,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124882917</v>
+        <v>124779232</v>
       </c>
       <c r="B17" t="n">
-        <v>79988</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95719</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,37 +2481,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229497</v>
+        <v>210</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos18, Vg</t>
+          <t>Smedstorp 1:1 pos54, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432235</v>
+        <v>431805</v>
       </c>
       <c r="R17" t="n">
-        <v>6427836</v>
+        <v>6427767</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2550,11 +2555,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2564,21 +2564,6 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2595,15 +2580,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124883045</v>
+        <v>124882863</v>
       </c>
       <c r="B18" t="n">
         <v>79456</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2634,14 +2614,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos 19, Vg</t>
+          <t>Middagsmärket 1:1 pos18, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>432154</v>
+        <v>432235</v>
       </c>
       <c r="R18" t="n">
-        <v>6427796</v>
+        <v>6427836</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2674,6 +2654,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2716,15 +2701,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124882863</v>
+        <v>124883045</v>
       </c>
       <c r="B19" t="n">
         <v>79456</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2755,14 +2735,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos18, Vg</t>
+          <t>Middagsmärker 1:1 pos 19, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432235</v>
+        <v>432154</v>
       </c>
       <c r="R19" t="n">
-        <v>6427836</v>
+        <v>6427796</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2795,11 +2775,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2842,37 +2817,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124882964</v>
+        <v>124883023</v>
       </c>
       <c r="B20" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79988</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2923,6 +2893,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På en hasselstam direkt intill den stora aspen med lunglav, ädellav och korallblylav (samma koordinat - se bilder för lunglaven).</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2935,17 +2910,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>hassel</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Corylus avellana</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Corylus avellana</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2963,37 +2938,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124911742</v>
+        <v>124911723</v>
       </c>
       <c r="B21" t="n">
-        <v>75009</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75017</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6439</v>
+        <v>308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3054,6 +3024,21 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
@@ -3069,15 +3054,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124911723</v>
+        <v>124911863</v>
       </c>
       <c r="B22" t="n">
-        <v>75017</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80073</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3085,21 +3065,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>308</v>
+        <v>229504</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3108,14 +3088,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos20, Vg</t>
+          <t>Middagsmärket 1:1 pos 123, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>432181</v>
+        <v>431964</v>
       </c>
       <c r="R22" t="n">
-        <v>6427847</v>
+        <v>6427784</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3162,17 +3142,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3190,15 +3170,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124911788</v>
+        <v>124911842</v>
       </c>
       <c r="B23" t="n">
         <v>79988</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3229,14 +3204,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 21, Vg</t>
+          <t>Middagsmärker 1:1 pos22, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>432143</v>
+        <v>431972</v>
       </c>
       <c r="R23" t="n">
-        <v>6427793</v>
+        <v>6427781</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3283,17 +3258,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3311,37 +3286,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124911863</v>
+        <v>124911865</v>
       </c>
       <c r="B24" t="n">
-        <v>80073</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229504</v>
+        <v>6431</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3350,14 +3320,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 123, Vg</t>
+          <t>Middagsmärket 1:1 pos25, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>431964</v>
+        <v>431886</v>
       </c>
       <c r="R24" t="n">
-        <v>6427784</v>
+        <v>6427693</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3404,17 +3374,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3432,37 +3402,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124911853</v>
+        <v>124911802</v>
       </c>
       <c r="B25" t="n">
-        <v>80073</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79988</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229504</v>
+        <v>229497</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3471,14 +3436,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos22, Vg</t>
+          <t>Middagsmärker 1:1 pos 19, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>431972</v>
+        <v>432154</v>
       </c>
       <c r="R25" t="n">
-        <v>6427781</v>
+        <v>6427796</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3525,17 +3490,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3553,37 +3518,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124911865</v>
+        <v>124911853</v>
       </c>
       <c r="B26" t="n">
-        <v>79327</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80073</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6431</v>
+        <v>229504</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3592,14 +3552,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos25, Vg</t>
+          <t>Middagsmärker 1:1 pos22, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>431886</v>
+        <v>431972</v>
       </c>
       <c r="R26" t="n">
-        <v>6427693</v>
+        <v>6427781</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3646,17 +3606,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3674,15 +3634,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124911784</v>
+        <v>124911788</v>
       </c>
       <c r="B27" t="n">
-        <v>95503</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79988</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3690,27 +3645,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2809</v>
+        <v>229497</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3756,11 +3710,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3770,6 +3719,21 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3786,15 +3750,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124911802</v>
+        <v>124911784</v>
       </c>
       <c r="B28" t="n">
-        <v>79988</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95503</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3802,37 +3761,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229497</v>
+        <v>2809</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos 19, Vg</t>
+          <t>Middagsmärket 1:1 pos 21, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>432154</v>
+        <v>432143</v>
       </c>
       <c r="R28" t="n">
-        <v>6427796</v>
+        <v>6427793</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3867,6 +3827,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3876,21 +3841,6 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3907,15 +3857,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124911842</v>
+        <v>124911742</v>
       </c>
       <c r="B29" t="n">
-        <v>79988</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75009</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3923,21 +3868,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>6439</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3946,14 +3891,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos22, Vg</t>
+          <t>Middagsmärket 1:1 pos20, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>431972</v>
+        <v>432181</v>
       </c>
       <c r="R29" t="n">
-        <v>6427781</v>
+        <v>6427847</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3997,21 +3942,6 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,61 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119783553</v>
+        <v>124779232</v>
       </c>
       <c r="B2" t="n">
-        <v>79051</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1026</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 6, Vg</t>
+          <t>Smedstorp 1:1 pos54, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432336</v>
+        <v>431805</v>
       </c>
       <c r="R2" t="n">
-        <v>6427848</v>
+        <v>6427767</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -756,12 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,26 +769,6 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -809,54 +785,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119803848</v>
+        <v>119813985</v>
       </c>
       <c r="B3" t="n">
-        <v>94218</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2755</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggsprötmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eurhynchium striatum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 7, Vg</t>
+          <t>Middagsmärket 1:1 pos 11, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>431908</v>
+        <v>432371</v>
       </c>
       <c r="R3" t="n">
-        <v>6427794</v>
+        <v>6427837</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -900,6 +870,26 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -916,15 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119803900</v>
+        <v>119814301</v>
       </c>
       <c r="B4" t="n">
-        <v>79668</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,21 +917,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229504</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -955,14 +940,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 8, Vg</t>
+          <t>Middagsmärket 1:1 pos 12, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>431942</v>
+        <v>432297</v>
       </c>
       <c r="R4" t="n">
-        <v>6427740</v>
+        <v>6427753</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1009,22 +994,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1042,37 +1027,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119803994</v>
+        <v>124911723</v>
       </c>
       <c r="B5" t="n">
-        <v>79583</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,14 +1061,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 10, Vg</t>
+          <t>Middagsmärket 1:1 pos20, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432217</v>
+        <v>432181</v>
       </c>
       <c r="R5" t="n">
-        <v>6427776</v>
+        <v>6427847</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1115,12 +1095,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,6 +1112,21 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1148,49 +1143,36 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119783586</v>
+        <v>119783315</v>
       </c>
       <c r="B6" t="n">
-        <v>79527</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79837</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>1026</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1243,7 +1225,11 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1282,53 +1268,60 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119803920</v>
+        <v>121871053</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1026</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 9, Vg</t>
+          <t>Smedstorp 1:1 pos2, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431951</v>
+        <v>432386</v>
       </c>
       <c r="R7" t="n">
-        <v>6427754</v>
+        <v>6427893</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1355,12 +1348,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,22 +1368,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>skogsek (aggregat)</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Quercus robur agg.</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Quercus robur agg.</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1408,53 +1396,60 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119783430</v>
+        <v>121871702</v>
       </c>
       <c r="B8" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79837</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1026</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 3, Vg</t>
+          <t>Smedstorp 1:1 pos6, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>432303</v>
+        <v>432304</v>
       </c>
       <c r="R8" t="n">
-        <v>6427851</v>
+        <v>6427870</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1481,12 +1476,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,6 +1493,21 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1514,37 +1524,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119783475</v>
+        <v>124882863</v>
       </c>
       <c r="B9" t="n">
-        <v>79583</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79837</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>1026</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1553,14 +1558,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos4, Vg</t>
+          <t>Middagsmärket 1:1 pos18, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>432309</v>
+        <v>432235</v>
       </c>
       <c r="R9" t="n">
-        <v>6427862</v>
+        <v>6427836</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1587,12 +1592,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,6 +1614,21 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1620,37 +1645,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119783544</v>
+        <v>124883045</v>
       </c>
       <c r="B10" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79837</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1026</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1659,14 +1679,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 5, Vg</t>
+          <t>Middagsmärker 1:1 pos 19, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432321</v>
+        <v>432154</v>
       </c>
       <c r="R10" t="n">
-        <v>6427859</v>
+        <v>6427796</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1693,12 +1713,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,14 +1741,9 @@
           <t>Populus tremula</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1746,15 +1761,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119814155</v>
+        <v>120967851</v>
       </c>
       <c r="B11" t="n">
-        <v>79583</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,48 +1772,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>1339</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 13, Vg</t>
+          <t>Middagsmärket, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>432326</v>
+        <v>432201</v>
       </c>
       <c r="R11" t="n">
-        <v>6427828</v>
+        <v>6427833</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1827,12 +1826,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1841,54 +1840,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna Pielach</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna Pielach</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119814486</v>
+        <v>119803848</v>
       </c>
       <c r="B12" t="n">
-        <v>94346</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96222</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,21 +1869,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2813</v>
+        <v>2755</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Skuggsprötmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Eurhynchium striatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1920,14 +1893,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 15, Vg</t>
+          <t>Middagsmärket 1:1 pos 7, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432226</v>
+        <v>431908</v>
       </c>
       <c r="R12" t="n">
-        <v>6427752</v>
+        <v>6427794</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1960,11 +1933,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>några få skott</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1992,15 +1960,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119814417</v>
+        <v>124911784</v>
       </c>
       <c r="B13" t="n">
-        <v>79583</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,45 +1971,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 14, Vg</t>
+          <t>Middagsmärket 1:1 pos 21, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432268</v>
+        <v>432143</v>
       </c>
       <c r="R13" t="n">
-        <v>6427731</v>
+        <v>6427793</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2073,12 +2029,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2090,26 +2051,6 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2126,15 +2067,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119814579</v>
+        <v>119814486</v>
       </c>
       <c r="B14" t="n">
-        <v>79527</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2142,37 +2078,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>2813</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 16, Vg</t>
+          <t>Middagsmärket 1:1 pos 15, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432354</v>
+        <v>432226</v>
       </c>
       <c r="R14" t="n">
-        <v>6427857</v>
+        <v>6427752</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2207,6 +2144,11 @@
           <t>2024-09-15</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>några få skott</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2216,26 +2158,6 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2252,15 +2174,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120967851</v>
+        <v>119783392</v>
       </c>
       <c r="B15" t="n">
-        <v>91324</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79707</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2268,37 +2185,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>6431</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Middagsmärket, Vg</t>
+          <t>Middagsmärket 1:1, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432201</v>
+        <v>432275</v>
       </c>
       <c r="R15" t="n">
-        <v>6427833</v>
+        <v>6427861</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2322,12 +2242,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2336,50 +2256,71 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124882964</v>
+        <v>124911865</v>
       </c>
       <c r="B16" t="n">
-        <v>80028</v>
+        <v>79707</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6431</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2388,14 +2329,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos18, Vg</t>
+          <t>Middagsmärket 1:1 pos25, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432235</v>
+        <v>431886</v>
       </c>
       <c r="R16" t="n">
-        <v>6427836</v>
+        <v>6427693</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2470,10 +2411,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124779232</v>
+        <v>121950204</v>
       </c>
       <c r="B17" t="n">
-        <v>95719</v>
+        <v>83290</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2481,46 +2422,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>210</v>
+        <v>6439</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Smedstorp 1:1 pos54, Vg</t>
+          <t>Smedstorp 1:1 pos31, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431805</v>
+        <v>432140</v>
       </c>
       <c r="R17" t="n">
-        <v>6427767</v>
+        <v>6427859</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2547,12 +2483,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2564,6 +2500,21 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2580,32 +2531,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124882863</v>
+        <v>124911742</v>
       </c>
       <c r="B18" t="n">
-        <v>79456</v>
+        <v>83290</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1026</v>
+        <v>6439</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2614,14 +2565,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos18, Vg</t>
+          <t>Middagsmärket 1:1 pos20, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>432235</v>
+        <v>432181</v>
       </c>
       <c r="R18" t="n">
-        <v>6427836</v>
+        <v>6427847</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2656,11 +2607,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2670,21 +2616,6 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2701,48 +2632,56 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124883045</v>
+        <v>119783586</v>
       </c>
       <c r="B19" t="n">
-        <v>79456</v>
+        <v>80336</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1026</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos 19, Vg</t>
+          <t>Middagsmärket 1:1 pos 6, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432154</v>
+        <v>432336</v>
       </c>
       <c r="R19" t="n">
-        <v>6427796</v>
+        <v>6427848</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2769,12 +2708,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2797,9 +2736,14 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2817,10 +2761,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124883023</v>
+        <v>119814579</v>
       </c>
       <c r="B20" t="n">
-        <v>79988</v>
+        <v>80336</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2828,21 +2772,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2851,14 +2795,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos18, Vg</t>
+          <t>Middagsmärket 1:1 pos 16, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>432235</v>
+        <v>432354</v>
       </c>
       <c r="R20" t="n">
-        <v>6427836</v>
+        <v>6427857</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2885,17 +2829,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På en hasselstam direkt intill den stora aspen med lunglav, ädellav och korallblylav (samma koordinat - se bilder för lunglaven).</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2910,17 +2849,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>hassel</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Corylus avellana</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Corylus avellana</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2938,48 +2882,56 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124911723</v>
+        <v>121950101</v>
       </c>
       <c r="B21" t="n">
-        <v>75017</v>
+        <v>80336</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos20, Vg</t>
+          <t>Smedstorp 1:1 pos30, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>432181</v>
+        <v>432130</v>
       </c>
       <c r="R21" t="n">
-        <v>6427847</v>
+        <v>6427867</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3006,12 +2958,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-01-03</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På samma asp som korallblylaven.  Torr kollekt var vitluddig på undersidan.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3026,17 +2983,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3054,10 +3011,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124911863</v>
+        <v>119783425</v>
       </c>
       <c r="B22" t="n">
-        <v>80073</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3065,21 +3022,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229504</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3088,14 +3045,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 123, Vg</t>
+          <t>Middagsmärket  1:1 pos 2, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431964</v>
+        <v>432289</v>
       </c>
       <c r="R22" t="n">
-        <v>6427784</v>
+        <v>6427861</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3122,12 +3079,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3142,17 +3099,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3170,32 +3132,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124911842</v>
+        <v>119783430</v>
       </c>
       <c r="B23" t="n">
-        <v>79988</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3204,14 +3166,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos22, Vg</t>
+          <t>Middagsmärket 1:1 pos 3, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431972</v>
+        <v>432303</v>
       </c>
       <c r="R23" t="n">
-        <v>6427781</v>
+        <v>6427851</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3238,12 +3200,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3255,21 +3217,6 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3286,32 +3233,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124911865</v>
+        <v>119783544</v>
       </c>
       <c r="B24" t="n">
-        <v>79327</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6431</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3320,14 +3267,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos25, Vg</t>
+          <t>Middagsmärket 1:1 pos 5, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>431886</v>
+        <v>432321</v>
       </c>
       <c r="R24" t="n">
-        <v>6427693</v>
+        <v>6427859</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3354,12 +3301,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3382,9 +3329,14 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3402,32 +3354,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124911802</v>
+        <v>119803920</v>
       </c>
       <c r="B25" t="n">
-        <v>79988</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3436,14 +3388,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos 19, Vg</t>
+          <t>Middagsmärket 1:1 pos 9, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>432154</v>
+        <v>431951</v>
       </c>
       <c r="R25" t="n">
-        <v>6427796</v>
+        <v>6427754</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3470,12 +3422,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3490,17 +3442,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>skogsek (aggregat)</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Quercus robur agg.</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark on living woody plant # Quercus robur agg.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3518,10 +3475,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124911853</v>
+        <v>121870994</v>
       </c>
       <c r="B26" t="n">
-        <v>80073</v>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3529,21 +3486,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229504</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3552,14 +3509,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Middagsmärker 1:1 pos22, Vg</t>
+          <t>Smedstorp 1:1, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>431972</v>
+        <v>432376</v>
       </c>
       <c r="R26" t="n">
-        <v>6427781</v>
+        <v>6427876</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3586,12 +3543,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3606,17 +3563,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3634,48 +3591,56 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124911788</v>
+        <v>121871661</v>
       </c>
       <c r="B27" t="n">
-        <v>79988</v>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 21, Vg</t>
+          <t>Smedstorp 1:1 pos5, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>432143</v>
+        <v>432317</v>
       </c>
       <c r="R27" t="n">
-        <v>6427793</v>
+        <v>6427873</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3702,12 +3667,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3750,49 +3715,56 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124911784</v>
+        <v>121949816</v>
       </c>
       <c r="B28" t="n">
-        <v>95503</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos 21, Vg</t>
+          <t>Smedstorp 1:1 pos29, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>432143</v>
+        <v>432061</v>
       </c>
       <c r="R28" t="n">
-        <v>6427793</v>
+        <v>6427847</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3819,17 +3791,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>på samma garn som brunpudrad nållav med samma koordinat</t>
+          <t>två små bålar på norra sidan stammen</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3841,6 +3813,21 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3857,48 +3844,52 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124911742</v>
+        <v>121950228</v>
       </c>
       <c r="B29" t="n">
-        <v>75009</v>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Middagsmärket 1:1 pos20, Vg</t>
+          <t>Smedstorp 1:1 pos57, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>432181</v>
+        <v>432225</v>
       </c>
       <c r="R29" t="n">
-        <v>6427847</v>
+        <v>6427874</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3925,12 +3916,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3943,6 +3934,21 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
@@ -3955,6 +3961,2170 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>124882964</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Middagsmärket 1:1 pos18, Vg</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>432235</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6427836</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>119783377</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Middagsmärket 1:1, Vg</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>432275</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6427861</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>119783407</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Middagsmärket  1:1 pos 2, Vg</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>432289</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6427861</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>119783475</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Middagsmärket 1:1 pos4, Vg</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>432309</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6427862</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>119803994</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Middagsmärket 1:1 pos 10, Vg</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>432217</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6427776</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>119814155</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Middagsmärket 1:1 pos 13, Vg</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>432326</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6427828</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>119814417</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Middagsmärket 1:1 pos 14, Vg</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>432268</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6427731</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>121871261</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Smedstorp 1:1 pos2, Vg</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>432386</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6427893</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>på norra sidan stammen, 0,5 m ovanför marken</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>121871747</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Smedstorp 1:1 pos6, Vg</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>432304</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6427870</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>121950090</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Smedstorp 1:1 pos30, Vg</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>432130</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6427867</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-01-03</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-01-03</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>många små bålar, det vänstra trädet på bilden</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>124882917</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Middagsmärket 1:1 pos18, Vg</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>432235</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6427836</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På samma asp som lunglav med samma koordinat (bild på trädet är laddat upp till rapporten för lunglaven)</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>124911788</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Middagsmärket 1:1 pos 21, Vg</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>432143</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6427793</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>124911802</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Middagsmärker 1:1 pos 19, Vg</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>432154</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6427796</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>124911842</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Middagsmärker 1:1 pos22, Vg</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>431972</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6427781</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>119783421</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Middagsmärket  1:1 pos 2, Vg</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>432289</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6427861</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>många små bålar</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>119803900</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Middagsmärket 1:1 pos 8, Vg</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>431942</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6427740</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>124911853</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Middagsmärker 1:1 pos22, Vg</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>431972</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6427781</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>124911863</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Middagsmärket 1:1 pos 123, Vg</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>431964</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6427784</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14606-2024 artfynd.xlsx
+++ b/artfynd/A 14606-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124779232</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119813985</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1024,6 +1039,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119814301</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124911723</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1265,6 +1290,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119783315</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1393,6 +1423,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121871053</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1521,6 +1556,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121871702</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1642,6 +1682,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124882863</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1758,6 +1803,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124883045</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1855,6 +1905,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120967851</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1957,6 +2012,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119803848</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2064,6 +2124,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124911784</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2171,6 +2236,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119814486</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2292,6 +2362,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119783392</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2408,6 +2483,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124911865</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2528,6 +2608,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121950204</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2629,6 +2714,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124911742</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2758,6 +2848,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119783586</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2879,6 +2974,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119814579</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3008,6 +3108,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121950101</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3129,6 +3234,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119783425</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3230,6 +3340,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119783430</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3351,6 +3466,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119783544</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3472,6 +3592,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119803920</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3588,6 +3713,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121870994</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3712,6 +3842,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121871661</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3841,6 +3976,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121949816</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3961,6 +4101,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121950228</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4077,6 +4222,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124882964</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4210,6 +4360,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119783377</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4339,6 +4494,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119783407</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4440,6 +4600,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119783475</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4541,6 +4706,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119803994</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4670,6 +4840,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119814155</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4799,6 +4974,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119814417</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4928,6 +5108,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121871261</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5052,6 +5237,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121871747</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5177,6 +5367,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121950090</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5298,6 +5493,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124882917</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5414,6 +5614,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124911788</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5530,6 +5735,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124911802</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5646,6 +5856,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124911842</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5772,6 +5987,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119783421</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5893,6 +6113,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119803900</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6009,6 +6234,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124911853</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6125,8 +6355,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124911863</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>